--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
         <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -960,10 +960,10 @@
         <v>2.44</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
         <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I6" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
         <v>3.15</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
         <v>1.73</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
         <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="K9" t="n">
         <v>2.88</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G11" t="n">
         <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
         <v>4.2</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G13" t="n">
         <v>2.98</v>
@@ -2909,34 +2909,34 @@
         <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
         <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
         <v>1.56</v>
@@ -2945,16 +2945,16 @@
         <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z13" t="n">
         <v>16.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB13" t="n">
         <v>10</v>
@@ -2987,22 +2987,22 @@
         <v>38</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
         <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR13" t="n">
         <v>14.5</v>
@@ -3020,41 +3020,41 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB13" t="n">
         <v>44</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>32</v>
       </c>
       <c r="BD13" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BE13" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="BF13" t="n">
         <v>36</v>
       </c>
       <c r="BG13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -3097,10 +3097,10 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2.18</v>
@@ -772,7 +772,7 @@
         <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.72</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="H3" t="n">
         <v>2.44</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="H4" t="n">
         <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
@@ -1178,7 +1178,7 @@
         <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J6" t="n">
         <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="n">
         <v>2.58</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
         <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="K9" t="n">
         <v>2.88</v>
@@ -2148,7 +2148,7 @@
         <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
         <v>4.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G13" t="n">
         <v>2.96</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.98</v>
       </c>
       <c r="H13" t="n">
         <v>2.74</v>
@@ -2915,13 +2915,13 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
         <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
         <v>2.32</v>
@@ -2936,34 +2936,34 @@
         <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
         <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA13" t="n">
         <v>46</v>
       </c>
       <c r="AB13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
         <v>7</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE13" t="n">
         <v>34</v>
@@ -2996,19 +2996,19 @@
         <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR13" t="n">
         <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3029,7 +3029,7 @@
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>46</v>
@@ -3038,7 +3038,7 @@
         <v>44</v>
       </c>
       <c r="BC13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD13" t="n">
         <v>48</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>13.5</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
         <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
         <v>1000</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
         <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
         <v>5.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD2" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5</v>
-      </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
         <v>4.7</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>2.72</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
         <v>2.44</v>
       </c>
       <c r="I3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J3" t="n">
         <v>3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
         <v>3.2</v>
@@ -1178,7 +1178,7 @@
         <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
         <v>3.65</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
         <v>3.4</v>
@@ -1736,7 +1736,7 @@
         <v>2.24</v>
       </c>
       <c r="I7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.3</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -2124,10 +2124,10 @@
         <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="K9" t="n">
         <v>2.88</v>
@@ -2142,13 +2142,13 @@
         <v>2.04</v>
       </c>
       <c r="O9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="P9" t="n">
         <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
         <v>2.9</v>
@@ -2318,7 +2318,7 @@
         <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
         <v>2.5</v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2420,16 +2420,16 @@
         <v>3.05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU10" t="n">
         <v>5.3</v>
@@ -2441,28 +2441,28 @@
         <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
         <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF10" t="n">
         <v>4.1</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         <v>2.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.89</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
@@ -2709,7 +2709,7 @@
         <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>4.6</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.94</v>
       </c>
       <c r="G13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H13" t="n">
         <v>2.74</v>
@@ -2918,7 +2918,7 @@
         <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
         <v>1.71</v>
@@ -2942,16 +2942,16 @@
         <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA13" t="n">
         <v>46</v>
@@ -3005,7 +3005,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
         <v>40</v>
@@ -3023,13 +3023,13 @@
         <v>32</v>
       </c>
       <c r="AX13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
         <v>46</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>1.18</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
         <v>1.37</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,72 +743,72 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Chiangrai Utd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>1.31</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.68</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
         <v>1000</v>
@@ -865,69 +865,69 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bangkok Utd</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.15</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Buriram Utd</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,42 +1325,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,123 +1393,123 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1.56</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.84</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.2</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>2.62</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2139,16 +2139,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.04</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.55</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,42 +2295,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>1.58</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,378 +2877,960 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>1.19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.5</v>
+        <v>1.15</v>
       </c>
       <c r="AS13" t="n">
-        <v>40</v>
+        <v>1.19</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>1.19</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>1.13</v>
       </c>
       <c r="AW13" t="n">
-        <v>32</v>
+        <v>1.19</v>
       </c>
       <c r="AX13" t="n">
-        <v>17</v>
+        <v>1.19</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>1.15</v>
       </c>
       <c r="BA13" t="n">
-        <v>46</v>
+        <v>1.19</v>
       </c>
       <c r="BB13" t="n">
-        <v>44</v>
+        <v>1.16</v>
       </c>
       <c r="BC13" t="n">
-        <v>34</v>
+        <v>1.16</v>
       </c>
       <c r="BD13" t="n">
-        <v>48</v>
+        <v>1.19</v>
       </c>
       <c r="BE13" t="n">
-        <v>110</v>
+        <v>1.19</v>
       </c>
       <c r="BF13" t="n">
-        <v>36</v>
+        <v>1.19</v>
       </c>
       <c r="BG13" t="n">
-        <v>32</v>
+        <v>1.19</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:04:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Forest Green</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:04:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:04:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Portuguese Primeira Liga</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Sporting Lisbon</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Tondela</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.17</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-04-27 07:47:48</t>
+      <c r="H17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM2" t="n">
         <v>110</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="K2" t="n">
-        <v>950</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -954,167 +954,167 @@
         <v>2.78</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="I3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.25</v>
       </c>
-      <c r="J3" t="n">
-        <v>2.96</v>
-      </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
         <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS3" t="n">
         <v>1.01</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AT3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA3" t="n">
         <v>1.01</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
         <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1145,136 +1145,136 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="J4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M4" t="n">
         <v>1.03</v>
       </c>
-      <c r="K4" t="n">
-        <v>950</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
         <v>1.01</v>
@@ -1283,7 +1283,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
         <v>1.01</v>
@@ -1304,11 +1304,11 @@
         <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.18</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.18</v>
+        <v>5.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.18</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.18</v>
+        <v>4.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.13</v>
+        <v>1.72</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.18</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.18</v>
+        <v>4.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.14</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.15</v>
+        <v>1.56</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>6.2</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>1.56</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2139,16 +2139,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3</v>
+        <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2891,28 +2891,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2933,10 +2933,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,10 +2957,10 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.19</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.19</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.15</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.19</v>
+        <v>2.98</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.19</v>
+        <v>5.3</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.13</v>
+        <v>3.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.19</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.19</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.15</v>
+        <v>3.95</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.16</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.16</v>
+        <v>4.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.19</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.19</v>
+        <v>4.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.19</v>
+        <v>4.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H14" t="n">
-        <v>1.28</v>
+        <v>3.75</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q14" t="n">
         <v>1.58</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.15</v>
+        <v>2.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I16" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>3.3</v>
@@ -3491,13 +3491,13 @@
         <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.45</v>
@@ -3509,22 +3509,22 @@
         <v>2.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
         <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
         <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
         <v>10.5</v>
@@ -3536,10 +3536,10 @@
         <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>7</v>
@@ -3548,34 +3548,34 @@
         <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO16" t="n">
         <v>38</v>
@@ -3584,16 +3584,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
@@ -3602,7 +3602,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX16" t="n">
         <v>17</v>
@@ -3614,29 +3614,29 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BC16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD16" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE16" t="n">
         <v>110</v>
       </c>
       <c r="BF16" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -781,22 +781,22 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.69</v>
@@ -805,25 +805,25 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
         <v>32</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -832,13 +832,13 @@
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
         <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -847,19 +847,19 @@
         <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
         <v>17.5</v>
@@ -874,22 +874,22 @@
         <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
@@ -898,29 +898,29 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
       </c>
       <c r="I3" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -999,10 +999,10 @@
         <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1068,7 +1068,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1092,29 +1092,29 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
         <v>17.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
         <v>1.5</v>
@@ -1184,7 +1184,7 @@
         <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1193,7 +1193,7 @@
         <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="W4" t="n">
         <v>1.13</v>
@@ -1202,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
         <v>12.5</v>
@@ -1220,7 +1220,7 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
         <v>75</v>
@@ -1235,7 +1235,7 @@
         <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK4" t="n">
         <v>100</v>
@@ -1247,68 +1247,68 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO4" t="n">
         <v>6.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="AS4" t="n">
         <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU4" t="n">
         <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>5.6</v>
@@ -1354,13 +1354,13 @@
         <v>2.94</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
         <v>2.34</v>
@@ -1369,10 +1369,10 @@
         <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
         <v>1.16</v>
@@ -1390,7 +1390,7 @@
         <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.7</v>
@@ -1456,25 +1456,25 @@
         <v>1.57</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AT5" t="n">
         <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
         <v>1.72</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.56</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
         <v>2.26</v>
@@ -1745,16 +1745,16 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
         <v>1.99</v>
@@ -1763,141 +1763,141 @@
         <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.85</v>
+        <v>8.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="I8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.82</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.2</v>
+        <v>2.44</v>
       </c>
       <c r="G9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="I10" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,184 +2683,184 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I12" t="n">
         <v>3.2</v>
       </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
       <c r="J12" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.02</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -2882,109 +2882,109 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P13" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
@@ -2999,69 +2999,69 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>1.47</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>1.53</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.98</v>
+        <v>1.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.3</v>
+        <v>1.55</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.7</v>
+        <v>1.46</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.3</v>
+        <v>1.53</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>1.45</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.3</v>
+        <v>1.55</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>1.52</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.1</v>
+        <v>1.52</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.1</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.3</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW14" t="n">
         <v>4.3</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>4.5</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.87</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.57</v>
-      </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,378 +3459,766 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>2.68</v>
+        <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Forest Green</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:29:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:29:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Portuguese Primeira Liga</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Sporting Lisbon</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Tondela</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" t="n">
         <v>1.16</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G19" t="n">
         <v>1.17</v>
       </c>
-      <c r="H17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I19" t="n">
         <v>25</v>
       </c>
-      <c r="J17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K19" t="n">
         <v>10.5</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1.37</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-04-27 12:16:49</t>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -784,7 +784,7 @@
         <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -868,25 +868,25 @@
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
@@ -895,32 +895,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1002,7 +1002,7 @@
         <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1059,62 +1059,62 @@
         <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR3" t="n">
         <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1175,16 +1175,16 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
         <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1253,25 +1253,25 @@
         <v>6.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
         <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU4" t="n">
         <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
         <v>11</v>
@@ -1286,7 +1286,7 @@
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB4" t="n">
         <v>5</v>
@@ -1304,11 +1304,11 @@
         <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.7</v>
@@ -1462,7 +1462,7 @@
         <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV5" t="n">
         <v>1.72</v>
@@ -1474,7 +1474,7 @@
         <v>4.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.56</v>
@@ -1486,7 +1486,7 @@
         <v>1.56</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BD5" t="n">
         <v>1.58</v>
@@ -1495,14 +1495,14 @@
         <v>1.42</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
         <v>1.61</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H6" t="n">
         <v>2.4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="J6" t="n">
         <v>2.9</v>
@@ -1551,7 +1551,7 @@
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1563,28 +1563,28 @@
         <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
@@ -1602,7 +1602,7 @@
         <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>14</v>
@@ -1650,7 +1650,7 @@
         <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
         <v>8.6</v>
@@ -1662,7 +1662,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
         <v>16.5</v>
@@ -1674,29 +1674,29 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
         <v>20</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H7" t="n">
         <v>3.55</v>
@@ -1778,7 +1778,7 @@
         <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H8" t="n">
         <v>1.46</v>
@@ -1957,7 +1957,7 @@
         <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S8" t="n">
         <v>2.08</v>
@@ -1966,10 +1966,10 @@
         <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
@@ -1978,25 +1978,25 @@
         <v>34</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AB8" t="n">
         <v>36</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AF8" t="n">
         <v>65</v>
@@ -2011,7 +2011,7 @@
         <v>26</v>
       </c>
       <c r="AJ8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AK8" t="n">
         <v>80</v>
@@ -2074,7 +2074,7 @@
         <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
         <v>8.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2145,10 +2145,10 @@
         <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
@@ -2172,7 +2172,7 @@
         <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
         <v>22</v>
@@ -2181,7 +2181,7 @@
         <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>44</v>
@@ -2211,7 +2211,7 @@
         <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
         <v>85</v>
@@ -2220,7 +2220,7 @@
         <v>21</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP9" t="n">
         <v>13.5</v>
@@ -2232,10 +2232,10 @@
         <v>18.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
@@ -2247,7 +2247,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
@@ -2256,29 +2256,29 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
         <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
         <v>16.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>3.95</v>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.26</v>
@@ -2345,16 +2345,16 @@
         <v>1.81</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.55</v>
@@ -2426,7 +2426,7 @@
         <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -2450,29 +2450,29 @@
         <v>10</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="BC10" t="n">
         <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>3.4</v>
@@ -2512,7 +2512,7 @@
         <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -2548,10 +2548,10 @@
         <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W11" t="n">
         <v>1.41</v>
@@ -2560,22 +2560,22 @@
         <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
         <v>32</v>
       </c>
       <c r="AB11" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>24</v>
@@ -2584,10 +2584,10 @@
         <v>26</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
         <v>36</v>
@@ -2608,7 +2608,7 @@
         <v>30</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AP11" t="n">
         <v>5.7</v>
@@ -2644,7 +2644,7 @@
         <v>5.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
         <v>6.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2730,7 +2730,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -2739,22 +2739,22 @@
         <v>2.86</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
@@ -2763,25 +2763,25 @@
         <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
         <v>42</v>
@@ -2805,62 +2805,62 @@
         <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G13" t="n">
         <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="K13" t="n">
         <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O13" t="n">
         <v>1.82</v>
@@ -2924,137 +2924,137 @@
         <v>1.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
         <v>1.47</v>
       </c>
       <c r="X13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE13" t="n">
         <v>7.8</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.55</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.32</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H14" t="n">
         <v>3.65</v>
@@ -3103,7 +3103,7 @@
         <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M14" t="n">
         <v>1.12</v>
@@ -3133,7 +3133,7 @@
         <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
         <v>1.58</v>
@@ -3205,7 +3205,7 @@
         <v>4.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AU14" t="n">
         <v>5.3</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
         <v>2.1</v>
@@ -3288,7 +3288,7 @@
         <v>3.9</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.65</v>
@@ -3300,13 +3300,13 @@
         <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -3315,16 +3315,16 @@
         <v>1.87</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
         <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3491,16 +3491,16 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
         <v>2.46</v>
@@ -3509,134 +3509,134 @@
         <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>1.87</v>
       </c>
       <c r="G17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I17" t="n">
         <v>4.2</v>
@@ -3685,16 +3685,16 @@
         <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
         <v>2.46</v>
@@ -3703,134 +3703,134 @@
         <v>1.57</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
         <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
@@ -3912,7 +3912,7 @@
         <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X18" t="n">
         <v>10.5</v>
@@ -3924,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB18" t="n">
         <v>9.800000000000001</v>
@@ -3936,10 +3936,10 @@
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
@@ -3951,7 +3951,7 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
         <v>40</v>
@@ -3960,10 +3960,10 @@
         <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO18" t="n">
         <v>36</v>
@@ -3972,7 +3972,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
         <v>14.5</v>
@@ -4002,13 +4002,13 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB18" t="n">
         <v>46</v>
       </c>
       <c r="BC18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD18" t="n">
         <v>50</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -4061,164 +4061,164 @@
         <v>1.17</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="I19" t="n">
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
         <v>10.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,10 +766,10 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -784,7 +784,7 @@
         <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -805,7 +805,7 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
         <v>1.29</v>
@@ -865,22 +865,22 @@
         <v>17.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
         <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
         <v>8</v>
@@ -916,11 +916,11 @@
         <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -999,10 +999,10 @@
         <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1059,19 +1059,19 @@
         <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
         <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
@@ -1089,7 +1089,7 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>4.9</v>
@@ -1110,11 +1110,11 @@
         <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
@@ -1175,16 +1175,16 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
         <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1220,7 +1220,7 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AF4" t="n">
         <v>75</v>
@@ -1247,68 +1247,68 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO4" t="n">
         <v>6.8</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT4" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY4" t="n">
         <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
         <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.57</v>
       </c>
-      <c r="AS5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="BA5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BF5" t="n">
         <v>3.95</v>
       </c>
-      <c r="AU5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ5" t="n">
+      <c r="BG5" t="n">
         <v>1.56</v>
       </c>
-      <c r="BA5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,148 +1524,148 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I6" t="n">
         <v>3.15</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.76</v>
-      </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="X6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y6" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>11</v>
-      </c>
       <c r="Z6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR6" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="AS6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU6" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
@@ -1674,29 +1674,29 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1775,43 +1775,43 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,69 +1835,69 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>8.4</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
-        <v>1.46</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.56</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>2.78</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.73</v>
       </c>
       <c r="X8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="I9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.15</v>
       </c>
-      <c r="J9" t="n">
+      <c r="O9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>3.55</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="AR9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY9" t="n">
         <v>3.95</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>22</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44</v>
+        <v>1.46</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.74</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>2.76</v>
       </c>
       <c r="W10" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI10" t="n">
         <v>26</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK10" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" t="n">
         <v>11</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.04</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.12</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.12</v>
+        <v>9.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.12</v>
+        <v>8.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.12</v>
+        <v>8.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.12</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
         <v>3.4</v>
@@ -2512,7 +2512,7 @@
         <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -2533,7 +2533,7 @@
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
         <v>1.67</v>
@@ -2551,7 +2551,7 @@
         <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W11" t="n">
         <v>1.41</v>
@@ -2590,7 +2590,7 @@
         <v>970</v>
       </c>
       <c r="AI11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ11" t="n">
         <v>60</v>
@@ -2599,7 +2599,7 @@
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>70</v>
@@ -2611,16 +2611,16 @@
         <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
         <v>5.2</v>
@@ -2635,13 +2635,13 @@
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BA11" t="n">
         <v>6.4</v>
@@ -2650,23 +2650,23 @@
         <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BD11" t="n">
         <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2721,7 +2721,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -2730,7 +2730,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -2745,10 +2745,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -2808,7 +2808,7 @@
         <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AR12" t="n">
         <v>4.1</v>
@@ -2817,13 +2817,13 @@
         <v>4.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
         <v>4.3</v>
@@ -2832,10 +2832,10 @@
         <v>4.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>4.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G13" t="n">
         <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
         <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
         <v>2.88</v>
@@ -2915,7 +2915,7 @@
         <v>1.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
         <v>1.82</v>
@@ -2948,7 +2948,7 @@
         <v>6</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z13" t="n">
         <v>21</v>
@@ -3008,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -3032,7 +3032,7 @@
         <v>6.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
         <v>7</v>
@@ -3041,20 +3041,20 @@
         <v>7</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
         <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>2.32</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
         <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
@@ -3106,13 +3106,13 @@
         <v>1.54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N14" t="n">
         <v>2.28</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P14" t="n">
         <v>1.42</v>
@@ -3121,7 +3121,7 @@
         <v>2.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
         <v>5.7</v>
@@ -3133,7 +3133,7 @@
         <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
         <v>1.58</v>
@@ -3166,7 +3166,7 @@
         <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
@@ -3205,28 +3205,28 @@
         <v>4.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
         <v>5.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB14" t="n">
         <v>4.2</v>
@@ -3241,14 +3241,14 @@
         <v>4.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3279,64 +3279,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
@@ -3345,25 +3345,25 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
@@ -3372,77 +3372,77 @@
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.5</v>
@@ -3509,7 +3509,7 @@
         <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S16" t="n">
         <v>2.38</v>
@@ -3518,7 +3518,7 @@
         <v>1.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
@@ -3536,7 +3536,7 @@
         <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
         <v>14.5</v>
@@ -3548,7 +3548,7 @@
         <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF16" t="n">
         <v>15.5</v>
@@ -3560,7 +3560,7 @@
         <v>16.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3590,7 +3590,7 @@
         <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>11.5</v>
@@ -3623,10 +3623,10 @@
         <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
         <v>7.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3679,19 +3679,19 @@
         <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
         <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
         <v>1.15</v>
@@ -3709,10 +3709,10 @@
         <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
         <v>1.31</v>
@@ -3769,22 +3769,22 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AQ17" t="n">
         <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AT17" t="n">
         <v>8.199999999999999</v>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -3808,7 +3808,7 @@
         <v>9.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BB17" t="n">
         <v>14</v>
@@ -3820,17 +3820,17 @@
         <v>16</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>3.35</v>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
@@ -3891,7 +3891,7 @@
         <v>1.45</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
         <v>2.38</v>
@@ -3906,19 +3906,19 @@
         <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V18" t="n">
         <v>1.58</v>
       </c>
       <c r="W18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
         <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18" t="n">
         <v>16</v>
@@ -3927,7 +3927,7 @@
         <v>42</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
         <v>7</v>
@@ -3945,7 +3945,7 @@
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
         <v>55</v>
@@ -3954,7 +3954,7 @@
         <v>50</v>
       </c>
       <c r="AK18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
@@ -3999,16 +3999,16 @@
         <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB18" t="n">
         <v>46</v>
       </c>
       <c r="BC18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD18" t="n">
         <v>50</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.16</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="H19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="I19" t="n">
         <v>25</v>
@@ -4070,155 +4070,543 @@
         <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P19" t="n">
         <v>3.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="S19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="X19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y19" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AD19" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AJ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AK19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AT19" t="n">
-        <v>1.48</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.6</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.63</v>
+        <v>7.8</v>
       </c>
       <c r="AY19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA19" t="n">
         <v>10</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BB19" t="n">
-        <v>1.41</v>
+        <v>7.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.63</v>
+        <v>2.52</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H2" t="n">
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -787,73 +787,73 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
         <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
         <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="n">
         <v>60</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -862,16 +862,16 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -883,44 +883,44 @@
         <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BG2" t="n">
         <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
@@ -999,7 +999,7 @@
         <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>1.44</v>
@@ -1032,7 +1032,7 @@
         <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>19.5</v>
@@ -1047,7 +1047,7 @@
         <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1065,19 +1065,19 @@
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
         <v>21</v>
@@ -1086,16 +1086,16 @@
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.8</v>
       </c>
       <c r="BC3" t="n">
         <v>5.1</v>
@@ -1104,17 +1104,17 @@
         <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
         <v>17.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1160,13 +1160,13 @@
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
         <v>5.3</v>
@@ -1175,16 +1175,16 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
         <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1220,7 +1220,7 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
         <v>75</v>
@@ -1247,13 +1247,13 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO4" t="n">
         <v>6.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>4</v>
@@ -1262,53 +1262,53 @@
         <v>3.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="AV4" t="n">
         <v>3.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
         <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
         <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1363,19 +1363,19 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q5" t="n">
         <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
         <v>5.8</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
         <v>1000</v>
@@ -1453,10 +1453,10 @@
         <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AT5" t="n">
         <v>4</v>
@@ -1465,10 +1465,10 @@
         <v>4.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AX5" t="n">
         <v>3.2</v>
@@ -1477,32 +1477,32 @@
         <v>3.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="BF5" t="n">
         <v>3.95</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -1853,7 +1853,7 @@
         <v>5.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>1.96</v>
       </c>
       <c r="AW7" t="n">
         <v>16.5</v>
@@ -1862,35 +1862,35 @@
         <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>1.99</v>
       </c>
       <c r="AZ7" t="n">
         <v>10</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BC7" t="n">
         <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
         <v>4.6</v>
@@ -1969,10 +1969,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J9" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2145,7 +2145,7 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
         <v>2.1</v>
@@ -2154,19 +2154,19 @@
         <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
         <v>13.5</v>
@@ -2223,62 +2223,62 @@
         <v>32</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>1.46</v>
@@ -2429,7 +2429,7 @@
         <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
         <v>9.4</v>
@@ -2438,7 +2438,7 @@
         <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         <v>6.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU11" t="n">
         <v>7.4</v>
@@ -2635,13 +2635,13 @@
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA11" t="n">
         <v>6.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2721,7 +2721,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -2730,7 +2730,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -2745,10 +2745,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -2808,7 +2808,7 @@
         <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AR12" t="n">
         <v>4.1</v>
@@ -2817,25 +2817,25 @@
         <v>4.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AW12" t="n">
         <v>4.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BA12" t="n">
         <v>4.4</v>
@@ -2856,11 +2856,11 @@
         <v>4.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G13" t="n">
         <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
         <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="K13" t="n">
         <v>2.88</v>
@@ -2957,10 +2957,10 @@
         <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
         <v>18</v>
@@ -3008,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -3020,7 +3020,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX13" t="n">
         <v>14.5</v>
@@ -3029,32 +3029,32 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3094,10 +3094,10 @@
         <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
@@ -3133,7 +3133,7 @@
         <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
         <v>1.58</v>
@@ -3166,7 +3166,7 @@
         <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3193,16 +3193,16 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
         <v>3.1</v>
@@ -3211,44 +3211,44 @@
         <v>5.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF14" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         <v>1.75</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y15" t="n">
         <v>18</v>
@@ -3351,7 +3351,7 @@
         <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE15" t="n">
         <v>55</v>
@@ -3393,7 +3393,7 @@
         <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
         <v>7.2</v>
@@ -3405,7 +3405,7 @@
         <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
         <v>40</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
         <v>4.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3691,28 +3691,28 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
         <v>1.57</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T17" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
         <v>1.31</v>
@@ -3733,7 +3733,7 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
         <v>15</v>
@@ -3748,7 +3748,7 @@
         <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH17" t="n">
         <v>23</v>
@@ -3769,13 +3769,13 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17" t="n">
         <v>12.5</v>
@@ -3784,7 +3784,7 @@
         <v>2.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AT17" t="n">
         <v>8.199999999999999</v>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -3808,7 +3808,7 @@
         <v>9.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BB17" t="n">
         <v>14</v>
@@ -3820,17 +3820,17 @@
         <v>16</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I18" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
@@ -3885,22 +3885,22 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
         <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
         <v>1.98</v>
@@ -3909,10 +3909,10 @@
         <v>1.97</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
         <v>10.5</v>
@@ -3933,13 +3933,13 @@
         <v>7</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
       </c>
       <c r="AF18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
@@ -3951,19 +3951,19 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO18" t="n">
         <v>36</v>
@@ -3978,7 +3978,7 @@
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT18" t="n">
         <v>9.4</v>
@@ -3996,7 +3996,7 @@
         <v>17</v>
       </c>
       <c r="AY18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
         <v>19</v>
@@ -4005,13 +4005,13 @@
         <v>46</v>
       </c>
       <c r="BB18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC18" t="n">
         <v>34</v>
       </c>
       <c r="BD18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE18" t="n">
         <v>110</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="G19" t="n">
         <v>1.16</v>
@@ -4067,7 +4067,7 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="K19" t="n">
         <v>11.5</v>
@@ -4091,7 +4091,7 @@
         <v>1.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S19" t="n">
         <v>1.89</v>
@@ -4100,7 +4100,7 @@
         <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
@@ -4136,10 +4136,10 @@
         <v>9.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
         <v>280</v>
@@ -4148,7 +4148,7 @@
         <v>9</v>
       </c>
       <c r="AK19" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
         <v>46</v>
@@ -4166,7 +4166,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR19" t="n">
         <v>10</v>
@@ -4181,10 +4181,10 @@
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="n">
         <v>7.8</v>
@@ -4214,11 +4214,11 @@
         <v>2.52</v>
       </c>
       <c r="BG19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -4273,16 +4273,16 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.33</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>1.42</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,201 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
         <v>4.3</v>
@@ -790,7 +790,7 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
         <v>1.41</v>
@@ -826,7 +826,7 @@
         <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>11.5</v>
@@ -838,7 +838,7 @@
         <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -898,29 +898,29 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>5.6</v>
       </c>
-      <c r="BE2" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF2" t="n">
-        <v>30</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
         <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>2.46</v>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -993,16 +993,16 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1068,7 +1068,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
         <v>4.9</v>
@@ -1104,17 +1104,17 @@
         <v>4.9</v>
       </c>
       <c r="BE3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF3" t="n">
         <v>5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
         <v>17.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1160,13 +1160,13 @@
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>5.3</v>
@@ -1175,16 +1175,16 @@
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
         <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1196,7 +1196,7 @@
         <v>2.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
         <v>29</v>
@@ -1220,7 +1220,7 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AF4" t="n">
         <v>75</v>
@@ -1247,68 +1247,68 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO4" t="n">
         <v>6.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU4" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9</v>
-      </c>
       <c r="AV4" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY4" t="n">
         <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
         <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AT5" t="n">
         <v>4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AX5" t="n">
         <v>3.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
         <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -1862,7 +1862,7 @@
         <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AZ7" t="n">
         <v>10</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
         <v>4.6</v>
@@ -1972,7 +1972,7 @@
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>2.9</v>
@@ -2133,7 +2133,7 @@
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2145,10 +2145,10 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.27</v>
@@ -2157,13 +2157,13 @@
         <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
         <v>1.35</v>
@@ -2223,7 +2223,7 @@
         <v>32</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
         <v>8</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
         <v>18.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="n">
         <v>1.46</v>
@@ -2429,7 +2429,7 @@
         <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>9.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         <v>6.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU11" t="n">
         <v>7.4</v>
@@ -2638,7 +2638,7 @@
         <v>6.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>5.7</v>
@@ -2650,7 +2650,7 @@
         <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>26</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
         <v>6.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2730,7 +2730,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -2745,10 +2745,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="P13" t="n">
         <v>1.33</v>
@@ -2951,28 +2951,28 @@
         <v>8.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF13" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH13" t="n">
         <v>34</v>
@@ -2981,10 +2981,10 @@
         <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="n">
         <v>140</v>
@@ -3008,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -3020,7 +3020,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
         <v>14.5</v>
@@ -3029,32 +3029,32 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
@@ -3205,7 +3205,7 @@
         <v>4.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AU14" t="n">
         <v>5.3</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -3321,7 +3321,7 @@
         <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
         <v>1.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.15</v>
@@ -3778,7 +3778,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>2.04</v>
       </c>
       <c r="AR17" t="n">
         <v>2.1</v>
@@ -3787,50 +3787,50 @@
         <v>2.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.97</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.4</v>
+        <v>1.92</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="AW17" t="n">
         <v>2.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="BA17" t="n">
         <v>2.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>2.06</v>
       </c>
       <c r="BC17" t="n">
-        <v>11</v>
+        <v>2.02</v>
       </c>
       <c r="BD17" t="n">
-        <v>16</v>
+        <v>2.08</v>
       </c>
       <c r="BE17" t="n">
         <v>2.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.6</v>
+        <v>1.88</v>
       </c>
       <c r="BG17" t="n">
         <v>2.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3978,10 +3978,10 @@
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>6.8</v>
@@ -4005,13 +4005,13 @@
         <v>46</v>
       </c>
       <c r="BB18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC18" t="n">
         <v>34</v>
       </c>
       <c r="BD18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE18" t="n">
         <v>110</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -4064,13 +4064,13 @@
         <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
         <v>10.5</v>
       </c>
       <c r="K19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4139,7 +4139,7 @@
         <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI19" t="n">
         <v>280</v>
@@ -4157,34 +4157,34 @@
         <v>270</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
         <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
         <v>7.8</v>
@@ -4193,10 +4193,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB19" t="n">
         <v>7.6</v>
@@ -4205,20 +4205,20 @@
         <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
         <v>2.52</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4664,19 +4664,19 @@
         <v>1.54</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
         <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4745,52 +4745,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -781,7 +781,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
@@ -790,7 +790,7 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R2" t="n">
         <v>1.41</v>
@@ -805,7 +805,7 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W2" t="n">
         <v>1.3</v>
@@ -817,19 +817,19 @@
         <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
         <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>22</v>
@@ -838,10 +838,10 @@
         <v>36</v>
       </c>
       <c r="AG2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>20</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>34</v>
@@ -901,26 +901,26 @@
         <v>5.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BG2" t="n">
         <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
       </c>
       <c r="I3" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -993,16 +993,16 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1181,10 +1181,10 @@
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1256,7 +1256,7 @@
         <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>9</v>
@@ -1265,13 +1265,13 @@
         <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="n">
         <v>3.95</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
         <v>4.3</v>
@@ -1280,13 +1280,13 @@
         <v>4.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AZ4" t="n">
         <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
         <v>4.9</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
         <v>3.3</v>
@@ -1363,13 +1363,13 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
         <v>2.7</v>
@@ -1381,7 +1381,7 @@
         <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
         <v>1.64</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AS5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AW5" t="n">
         <v>1.39</v>
       </c>
-      <c r="AT5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AX5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AZ5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA5" t="n">
         <v>1.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.39</v>
       </c>
       <c r="BB5" t="n">
         <v>1.34</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1563,13 +1563,13 @@
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
         <v>3.1</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1757,10 +1757,10 @@
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
         <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>1.71</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
         <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
         <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
         <v>11</v>
@@ -2214,22 +2214,22 @@
         <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO9" t="n">
         <v>32</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
         <v>4.8</v>
@@ -2247,7 +2247,7 @@
         <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2265,10 +2265,10 @@
         <v>4.8</v>
       </c>
       <c r="BD9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5</v>
       </c>
       <c r="BF9" t="n">
         <v>4.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q10" t="n">
         <v>1.44</v>
@@ -2438,7 +2438,7 @@
         <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G11" t="n">
         <v>3.4</v>
@@ -2512,7 +2512,7 @@
         <v>2.24</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -2551,7 +2551,7 @@
         <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
         <v>1.41</v>
@@ -2587,7 +2587,7 @@
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>34</v>
@@ -2611,7 +2611,7 @@
         <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
         <v>11.5</v>
@@ -2620,10 +2620,10 @@
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU11" t="n">
         <v>7.4</v>
@@ -2635,38 +2635,38 @@
         <v>17</v>
       </c>
       <c r="AX11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2748,7 +2748,7 @@
         <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -2844,7 +2844,7 @@
         <v>4.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD12" t="n">
         <v>4.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
         <v>3.1</v>
@@ -2900,7 +2900,7 @@
         <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
         <v>2.62</v>
@@ -2909,19 +2909,19 @@
         <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M13" t="n">
         <v>1.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="P13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
         <v>3.5</v>
@@ -2933,19 +2933,19 @@
         <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
         <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y13" t="n">
         <v>8.6</v>
@@ -2954,49 +2954,49 @@
         <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
         <v>18.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM13" t="n">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AN13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
         <v>5.3</v>
@@ -3008,53 +3008,53 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G14" t="n">
         <v>2.72</v>
@@ -3112,22 +3112,22 @@
         <v>2.28</v>
       </c>
       <c r="O14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="P14" t="n">
         <v>1.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U14" t="n">
         <v>1.64</v>
@@ -3151,7 +3151,7 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
         <v>8.4</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
         <v>5.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF14" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.5</v>
@@ -3500,7 +3500,7 @@
         <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
         <v>2.46</v>
@@ -3587,7 +3587,7 @@
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
         <v>8.199999999999999</v>
@@ -3623,7 +3623,7 @@
         <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16" t="n">
         <v>8</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
         <v>15</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT17" t="n">
         <v>2.04</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AU17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AV17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AS17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AW17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
         <v>7</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="G19" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H19" t="n">
         <v>21</v>
@@ -4070,7 +4070,7 @@
         <v>10.5</v>
       </c>
       <c r="K19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4100,7 +4100,7 @@
         <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
@@ -4109,10 +4109,10 @@
         <v>7.2</v>
       </c>
       <c r="X19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Z19" t="n">
         <v>280</v>
@@ -4124,10 +4124,10 @@
         <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AD19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
@@ -4136,7 +4136,7 @@
         <v>9.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
         <v>55</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS19" t="n">
         <v>11</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
         <v>11</v>
@@ -4181,10 +4181,10 @@
         <v>17.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX19" t="n">
         <v>7.8</v>
@@ -4193,10 +4193,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.4</v>
+        <v>44</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
         <v>7.6</v>
@@ -4205,20 +4205,20 @@
         <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
         <v>2.52</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,201 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -766,7 +766,7 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -796,7 +796,7 @@
         <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T2" t="n">
         <v>1.7</v>
@@ -805,7 +805,7 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W2" t="n">
         <v>1.3</v>
@@ -898,10 +898,10 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
         <v>32</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -978,7 +978,7 @@
         <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
         <v>1.89</v>
@@ -987,22 +987,22 @@
         <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1014,7 +1014,7 @@
         <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB3" t="n">
         <v>14</v>
@@ -1029,7 +1029,7 @@
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1041,13 +1041,13 @@
         <v>48</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1059,7 +1059,7 @@
         <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.4</v>
@@ -1068,7 +1068,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1080,7 +1080,7 @@
         <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1092,29 +1092,29 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
         <v>17.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>6.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I4" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
@@ -1181,10 +1181,10 @@
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1193,52 +1193,52 @@
         <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="W4" t="n">
         <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>17.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ4" t="n">
         <v>210</v>
       </c>
       <c r="AK4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="n">
         <v>85</v>
@@ -1247,68 +1247,68 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU4" t="n">
         <v>5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.95</v>
       </c>
       <c r="AV4" t="n">
         <v>8</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
         <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
         <v>5.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
         <v>2.6</v>
@@ -1542,7 +1542,7 @@
         <v>2.92</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
@@ -1551,7 +1551,7 @@
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1560,28 +1560,28 @@
         <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
         <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>1.62</v>
@@ -1596,7 +1596,7 @@
         <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
@@ -1617,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
         <v>44</v>
@@ -1671,7 +1671,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
         <v>9.199999999999999</v>
@@ -1680,7 +1680,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
         <v>9</v>
@@ -1692,11 +1692,11 @@
         <v>16.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1730,31 +1730,31 @@
         <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
         <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
         <v>1.98</v>
@@ -1763,134 +1763,134 @@
         <v>1.82</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO7" t="n">
         <v>26</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AP7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF7" t="n">
         <v>18.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BG7" t="n">
-        <v>2.16</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
         <v>2.36</v>
@@ -1969,7 +1969,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
         <v>1.73</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2115,46 +2115,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G9" t="n">
         <v>3.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="J9" t="n">
         <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2163,16 +2163,16 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
         <v>18.5</v>
@@ -2202,40 +2202,40 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
         <v>70</v>
       </c>
       <c r="AK9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.4</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
         <v>16.5</v>
@@ -2253,32 +2253,32 @@
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
         <v>1.46</v>
@@ -2324,7 +2324,7 @@
         <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.2</v>
@@ -2348,16 +2348,16 @@
         <v>1.74</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
         <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
@@ -2420,10 +2420,10 @@
         <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
         <v>11</v>
@@ -2441,7 +2441,7 @@
         <v>6.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="AY10" t="n">
         <v>7.2</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -2536,28 +2536,28 @@
         <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
         <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
         <v>970</v>
@@ -2623,10 +2623,10 @@
         <v>6.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
         <v>6.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>5.8</v>
@@ -2662,11 +2662,11 @@
         <v>6.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
         <v>2.6</v>
@@ -2712,16 +2712,16 @@
         <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -2730,7 +2730,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -2739,16 +2739,16 @@
         <v>2.86</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -2796,7 +2796,7 @@
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
         <v>22</v>
@@ -2820,7 +2820,7 @@
         <v>3.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AV12" t="n">
         <v>3.8</v>
@@ -2841,10 +2841,10 @@
         <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD12" t="n">
         <v>4.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G13" t="n">
         <v>3.1</v>
@@ -2900,25 +2900,25 @@
         <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K13" t="n">
         <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
         <v>1.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="P13" t="n">
         <v>1.34</v>
@@ -2933,19 +2933,19 @@
         <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
         <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
         <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="n">
         <v>8.6</v>
@@ -2963,13 +2963,13 @@
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
         <v>18.5</v>
@@ -2996,65 +2996,65 @@
         <v>95</v>
       </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB13" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB13" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BC13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>2.5</v>
@@ -3109,7 +3109,7 @@
         <v>1.13</v>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.65</v>
@@ -3118,10 +3118,10 @@
         <v>1.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
         <v>5.6</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
         <v>2.14</v>
@@ -3288,7 +3288,7 @@
         <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
@@ -3321,16 +3321,16 @@
         <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
@@ -3399,7 +3399,7 @@
         <v>7.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3414,7 +3414,7 @@
         <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>15</v>
@@ -3429,20 +3429,20 @@
         <v>18.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
         <v>7.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG15" t="n">
         <v>34</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
         <v>3.75</v>
@@ -3491,13 +3491,13 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
@@ -3524,7 +3524,7 @@
         <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X16" t="n">
         <v>26</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
         <v>2.06</v>
@@ -3691,10 +3691,10 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
         <v>2.44</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA18" t="n">
         <v>42</v>
@@ -3933,7 +3933,7 @@
         <v>7</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
@@ -3960,7 +3960,7 @@
         <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
         <v>44</v>
@@ -3969,7 +3969,7 @@
         <v>36</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
         <v>8.800000000000001</v>
@@ -3978,7 +3978,7 @@
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT18" t="n">
         <v>9.800000000000001</v>
@@ -3999,19 +3999,19 @@
         <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
         <v>46</v>
       </c>
       <c r="BB18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC18" t="n">
         <v>34</v>
       </c>
       <c r="BD18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE18" t="n">
         <v>110</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4064,10 +4064,10 @@
         <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
         <v>13</v>
@@ -4094,19 +4094,19 @@
         <v>1.94</v>
       </c>
       <c r="S19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T19" t="n">
         <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="X19" t="n">
         <v>55</v>
@@ -4124,16 +4124,16 @@
         <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AD19" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG19" t="n">
         <v>14.5</v>
@@ -4154,7 +4154,7 @@
         <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AN19" t="n">
         <v>2.82</v>
@@ -4166,7 +4166,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
         <v>10.5</v>
@@ -4205,7 +4205,7 @@
         <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE19" t="n">
         <v>10.5</v>
@@ -4214,11 +4214,11 @@
         <v>2.52</v>
       </c>
       <c r="BG19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4637,170 +4637,170 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="I22" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K22" t="n">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>2.68</v>
       </c>
       <c r="O22" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
         <v>2.06</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V22" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -790,13 +790,13 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.7</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -969,10 +969,10 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>3.6</v>
@@ -987,16 +987,16 @@
         <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.55</v>
@@ -1014,7 +1014,7 @@
         <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="n">
         <v>14</v>
@@ -1029,7 +1029,7 @@
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1041,13 +1041,13 @@
         <v>48</v>
       </c>
       <c r="AJ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL3" t="n">
         <v>50</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1065,10 +1065,10 @@
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.4</v>
@@ -1080,41 +1080,41 @@
         <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF3" t="n">
         <v>5</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG3" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
         <v>2.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
         <v>26</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
         <v>5.6</v>
@@ -1354,7 +1354,7 @@
         <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
         <v>1.56</v>
@@ -1363,16 +1363,16 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P5" t="n">
         <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.16</v>
@@ -1381,7 +1381,7 @@
         <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
         <v>1.64</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
         <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AT5" t="n">
         <v>4.1</v>
@@ -1465,44 +1465,44 @@
         <v>4.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1563,7 +1563,7 @@
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
         <v>1.86</v>
@@ -1572,7 +1572,7 @@
         <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
         <v>1.7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
         <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
@@ -1769,16 +1769,16 @@
         <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>19.5</v>
@@ -1838,46 +1838,46 @@
         <v>11.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
         <v>4.1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
         <v>1.73</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2118,22 +2118,22 @@
         <v>2.96</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
         <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -2142,19 +2142,19 @@
         <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
         <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2163,7 +2163,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
         <v>1.34</v>
@@ -2223,7 +2223,7 @@
         <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>7.8</v>
@@ -2232,10 +2232,10 @@
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.4</v>
@@ -2244,10 +2244,10 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2256,13 +2256,13 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
         <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
         <v>4.9</v>
@@ -2271,14 +2271,14 @@
         <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="J10" t="n">
         <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.2</v>
@@ -2345,22 +2345,22 @@
         <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S10" t="n">
         <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
         <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>34</v>
@@ -2414,10 +2414,10 @@
         <v>65</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>11.5</v>
@@ -2429,7 +2429,7 @@
         <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AU10" t="n">
         <v>9.4</v>
@@ -2438,41 +2438,41 @@
         <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>6.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD10" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF10" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.6</v>
       </c>
       <c r="BG10" t="n">
         <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>3.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
         <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -2551,7 +2551,7 @@
         <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W11" t="n">
         <v>1.43</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
@@ -2730,7 +2730,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -2739,16 +2739,16 @@
         <v>2.86</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
         <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -2796,7 +2796,7 @@
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
         <v>22</v>
@@ -2811,46 +2811,46 @@
         <v>3.85</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
         <v>3.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV12" t="n">
         <v>3.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY12" t="n">
         <v>3.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BA12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
         <v>4.1</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
         <v>120</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -3017,19 +3017,19 @@
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
         <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
         <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BA13" t="n">
         <v>8.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L14" t="n">
         <v>1.54</v>
@@ -3112,13 +3112,13 @@
         <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="R14" t="n">
         <v>1.15</v>
@@ -3130,13 +3130,13 @@
         <v>2.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
         <v>8.6</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AU14" t="n">
         <v>5.3</v>
       </c>
       <c r="AV14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX14" t="n">
         <v>4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.8</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3282,22 +3282,22 @@
         <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
         <v>3.85</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3327,7 +3327,7 @@
         <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
         <v>1.89</v>
@@ -3432,7 +3432,7 @@
         <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>12.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>3.75</v>
@@ -3491,7 +3491,7 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
@@ -3521,10 +3521,10 @@
         <v>2.46</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
         <v>26</v>
@@ -3569,7 +3569,7 @@
         <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM16" t="n">
         <v>65</v>
@@ -3602,7 +3602,7 @@
         <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
@@ -3614,7 +3614,7 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
         <v>18.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
@@ -3697,7 +3697,7 @@
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
         <v>1.57</v>
@@ -3718,7 +3718,7 @@
         <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
         <v>26</v>
@@ -3769,22 +3769,22 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.14</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AT17" t="n">
         <v>2.04</v>
@@ -3796,7 +3796,7 @@
         <v>2.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AX17" t="n">
         <v>2.06</v>
@@ -3808,7 +3808,7 @@
         <v>2.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BB17" t="n">
         <v>2.14</v>
@@ -3820,17 +3820,17 @@
         <v>2.16</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BF17" t="n">
         <v>1.95</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3867,10 +3867,10 @@
         <v>3.1</v>
       </c>
       <c r="H18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I18" t="n">
         <v>2.66</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.68</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
@@ -3894,13 +3894,13 @@
         <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
         <v>1.98</v>
@@ -3909,10 +3909,10 @@
         <v>1.97</v>
       </c>
       <c r="V18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
         <v>10.5</v>
@@ -3933,13 +3933,13 @@
         <v>7</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
@@ -3966,7 +3966,7 @@
         <v>44</v>
       </c>
       <c r="AO18" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP18" t="n">
         <v>10</v>
@@ -3999,13 +3999,13 @@
         <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB18" t="n">
         <v>46</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>44</v>
       </c>
       <c r="BC18" t="n">
         <v>34</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4055,31 +4055,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>1.12</v>
@@ -4091,22 +4091,22 @@
         <v>1.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="X19" t="n">
         <v>55</v>
@@ -4121,19 +4121,19 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AD19" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG19" t="n">
         <v>14.5</v>
@@ -4142,7 +4142,7 @@
         <v>55</v>
       </c>
       <c r="AI19" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AJ19" t="n">
         <v>9</v>
@@ -4154,37 +4154,37 @@
         <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AN19" t="n">
         <v>2.82</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
         <v>7.8</v>
@@ -4193,10 +4193,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB19" t="n">
         <v>7.6</v>
@@ -4205,20 +4205,20 @@
         <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="BE19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
@@ -4264,7 +4264,7 @@
         <v>1.09</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4288,7 +4288,7 @@
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>1.42</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>5.7</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4667,16 +4667,16 @@
         <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="T22" t="n">
         <v>1.98</v>
@@ -4691,10 +4691,10 @@
         <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
         <v>40</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
         <v>23</v>
@@ -4715,10 +4715,10 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
         <v>26</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="G23" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="I23" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>2.78</v>
       </c>
       <c r="K23" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="O23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S23" t="n">
         <v>1.02</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.18</v>
-      </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V23" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -766,7 +766,7 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -805,7 +805,7 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W2" t="n">
         <v>1.3</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,7 +978,7 @@
         <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.89</v>
@@ -993,10 +993,10 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
         <v>1.55</v>
@@ -1071,16 +1071,16 @@
         <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1089,7 +1089,7 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>4.9</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.47</v>
       </c>
       <c r="I4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
@@ -1193,7 +1193,7 @@
         <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="W4" t="n">
         <v>1.15</v>
@@ -1268,25 +1268,25 @@
         <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
         <v>5.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>7.8</v>
@@ -1295,7 +1295,7 @@
         <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
         <v>7.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="K5" t="n">
         <v>3.25</v>
@@ -1363,19 +1363,19 @@
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
         <v>1.63</v>
       </c>
       <c r="P5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
         <v>5.8</v>
@@ -1453,10 +1453,10 @@
         <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AT5" t="n">
         <v>4.1</v>
@@ -1465,44 +1465,44 @@
         <v>4.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I6" t="n">
         <v>3.1</v>
@@ -1548,7 +1548,7 @@
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.31</v>
@@ -1557,7 +1557,7 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
         <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.35</v>
@@ -1745,43 +1745,43 @@
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
         <v>14.5</v>
@@ -1796,7 +1796,7 @@
         <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>15</v>
@@ -1814,13 +1814,13 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
         <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="n">
         <v>50</v>
@@ -1832,7 +1832,7 @@
         <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
         <v>11.5</v>
@@ -1844,7 +1844,7 @@
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
         <v>10.5</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
         <v>17</v>
@@ -1865,10 +1865,10 @@
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
         <v>4.2</v>
@@ -1880,17 +1880,17 @@
         <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G8" t="n">
         <v>2.36</v>
@@ -1942,19 +1942,19 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
         <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
@@ -1969,7 +1969,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
         <v>1.73</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>3.85</v>
       </c>
       <c r="H9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
         <v>2.88</v>
@@ -2130,10 +2130,10 @@
         <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -2145,16 +2145,16 @@
         <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2163,10 +2163,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
@@ -2175,13 +2175,13 @@
         <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
         <v>44</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.6</v>
@@ -2193,7 +2193,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>16.5</v>
@@ -2223,40 +2223,40 @@
         <v>34</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>3.55</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.4</v>
+        <v>3.75</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
         <v>18.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB9" t="n">
         <v>4.9</v>
@@ -2268,17 +2268,17 @@
         <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="I10" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.2</v>
@@ -2351,16 +2351,16 @@
         <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>34</v>
@@ -2369,7 +2369,7 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
         <v>970</v>
@@ -2399,7 +2399,7 @@
         <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AK10" t="n">
         <v>80</v>
@@ -2414,19 +2414,19 @@
         <v>65</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>24</v>
@@ -2438,41 +2438,41 @@
         <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC10" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BG10" t="n">
         <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -2551,7 +2551,7 @@
         <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
         <v>1.43</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
@@ -2715,7 +2715,7 @@
         <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -2730,28 +2730,28 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T12" t="n">
         <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
         <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -2796,7 +2796,7 @@
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
         <v>22</v>
@@ -2817,7 +2817,7 @@
         <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AU12" t="n">
         <v>3.35</v>
@@ -2844,7 +2844,7 @@
         <v>4.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD12" t="n">
         <v>4.5</v>
@@ -2856,11 +2856,11 @@
         <v>4.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>2.82</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
         <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
         <v>2.64</v>
@@ -2909,7 +2909,7 @@
         <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M13" t="n">
         <v>1.19</v>
@@ -2933,16 +2933,16 @@
         <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U13" t="n">
         <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
         <v>6</v>
@@ -2960,13 +2960,13 @@
         <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="n">
         <v>19</v>
@@ -2999,16 +2999,16 @@
         <v>120</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
         <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
         <v>6.2</v>
@@ -3017,44 +3017,44 @@
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX13" t="n">
         <v>14.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ13" t="n">
         <v>24</v>
       </c>
       <c r="BA13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF13" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE13" t="n">
+      <c r="BG13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H14" t="n">
         <v>3.65</v>
@@ -3097,7 +3097,7 @@
         <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="K14" t="n">
         <v>3.15</v>
@@ -3106,43 +3106,43 @@
         <v>1.54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N14" t="n">
         <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P14" t="n">
         <v>1.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
         <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
         <v>1.65</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY14" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU14" t="n">
+      <c r="AZ14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE14" t="n">
         <v>5.3</v>
       </c>
-      <c r="AV14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG14" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -3393,7 +3393,7 @@
         <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS15" t="n">
         <v>7.2</v>
@@ -3432,7 +3432,7 @@
         <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
         <v>12.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>1.86</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
         <v>4.3</v>
@@ -3691,7 +3691,7 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.18</v>
@@ -3718,7 +3718,7 @@
         <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3739,7 +3739,7 @@
         <v>15</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AR17" t="n">
         <v>2.18</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AW17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BA17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BB17" t="n">
         <v>2.14</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3867,10 +3867,10 @@
         <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I18" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
@@ -3891,10 +3891,10 @@
         <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
@@ -3903,28 +3903,28 @@
         <v>4.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U18" t="n">
         <v>1.97</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
         <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
         <v>15.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
         <v>10</v>
@@ -3936,7 +3936,7 @@
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF18" t="n">
         <v>18.5</v>
@@ -3951,7 +3951,7 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
         <v>40</v>
@@ -3963,7 +3963,7 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO18" t="n">
         <v>32</v>
@@ -3990,10 +3990,10 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -4005,7 +4005,7 @@
         <v>48</v>
       </c>
       <c r="BB18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC18" t="n">
         <v>34</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4055,67 +4055,67 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.15</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.16</v>
-      </c>
       <c r="H19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="K19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>1.12</v>
       </c>
       <c r="P19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R19" t="n">
         <v>1.95</v>
       </c>
       <c r="S19" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="X19" t="n">
         <v>55</v>
       </c>
       <c r="Y19" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Z19" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -4127,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="AD19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AE19" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG19" t="n">
         <v>14.5</v>
@@ -4145,10 +4145,10 @@
         <v>290</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AL19" t="n">
         <v>46</v>
@@ -4160,43 +4160,43 @@
         <v>2.82</v>
       </c>
       <c r="AO19" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX19" t="n">
         <v>7.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB19" t="n">
         <v>7.6</v>
@@ -4208,17 +4208,17 @@
         <v>36</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
@@ -4264,7 +4264,7 @@
         <v>1.09</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,22 +4273,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -4297,7 +4297,7 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1.42</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -4470,19 +4470,19 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P21" t="n">
         <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="H22" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="X22" t="n">
         <v>970</v>
@@ -4697,7 +4697,7 @@
         <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4709,7 +4709,7 @@
         <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4721,86 +4721,86 @@
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU22" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AV22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX22" t="n">
         <v>3.9</v>
       </c>
-      <c r="AR22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT22" t="n">
+      <c r="AY22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE22" t="n">
-        <v>3.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.9</v>
+        <v>1.53</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4864,19 +4864,19 @@
         <v>1.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R23" t="n">
         <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
         <v>1.21</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Chiangrai Utd</t>
+          <t>Xian Chongde Ronghai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Dalian Yingbo II</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.79</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Guangzhou Alpha</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bangkok Utd</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.76</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="H3" t="n">
-        <v>2.46</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>2.82</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
         <v>21</v>
       </c>
-      <c r="AA3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
         <v>14</v>
       </c>
-      <c r="AC3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>24</v>
-      </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>05:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>Hubei Istar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buriram Utd</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>1.56</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>2.78</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,72 +1325,72 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Shanghai Second</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.8</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Chiangrai Utd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.94</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V6" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.47</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW6" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>12</v>
       </c>
-      <c r="AC6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AZ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG6" t="n">
         <v>9.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>22</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Ganzhou Ruishi FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Xiamen Feilu</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>1.32</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,126 +1907,126 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP8" t="n">
         <v>1.03</v>
@@ -2077,21 +2077,21 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,159 +2101,159 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Bangkok Utd</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="G9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.85</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.71</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y9" t="n">
         <v>13</v>
       </c>
-      <c r="Y9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL9" t="n">
         <v>55</v>
       </c>
-      <c r="AL9" t="n">
-        <v>70</v>
-      </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
         <v>4.8</v>
@@ -2262,30 +2262,30 @@
         <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
         <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>1.89</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>2.44</v>
       </c>
       <c r="H10" t="n">
-        <v>1.49</v>
+        <v>3.55</v>
       </c>
       <c r="I10" t="n">
-        <v>1.52</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.02</v>
       </c>
-      <c r="N10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.15</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.84</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>2.92</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="X10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Buriram Utd</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="I11" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
         <v>970</v>
       </c>
       <c r="Z11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>970</v>
       </c>
-      <c r="AA11" t="n">
-        <v>32</v>
-      </c>
       <c r="AB11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
         <v>970</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AU11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY12" t="n">
         <v>3.9</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>3.95</v>
+        <v>1.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.5</v>
+        <v>1.19</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.5</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.3</v>
+        <v>1.16</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>1.18</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>1.19</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>AS Solimane</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>2.88</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="O13" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>1.02</v>
       </c>
       <c r="T13" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,75 +3071,75 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>US Monastirienne</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>AS Gabes</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="O14" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3193,69 +3193,69 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>7.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>1.48</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>2.92</v>
       </c>
       <c r="W15" t="n">
-        <v>1.89</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>65</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="n">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AP15" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV15" t="n">
         <v>9</v>
       </c>
-      <c r="AU15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AW15" t="n">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>2.36</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.58</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="X16" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>22</v>
       </c>
-      <c r="Z16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AL16" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17.5</v>
+        <v>3.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.6</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>3.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.18</v>
+        <v>16.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.08</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.12</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.08</v>
+        <v>8.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.02</v>
+        <v>6.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.14</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.14</v>
+        <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="G18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.1</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.6</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB18" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>10</v>
-      </c>
       <c r="AC18" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
       </c>
       <c r="AF18" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
         <v>20</v>
       </c>
       <c r="AI18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>50</v>
       </c>
       <c r="AK18" t="n">
         <v>40</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>10</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>36</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF18" t="n">
         <v>19</v>
       </c>
-      <c r="BA18" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>40</v>
-      </c>
       <c r="BG18" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.13</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1.15</v>
+        <v>2.6</v>
       </c>
       <c r="H19" t="n">
-        <v>24</v>
+        <v>2.94</v>
       </c>
       <c r="I19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB19" t="n">
         <v>30</v>
       </c>
-      <c r="J19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>290</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>450</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
+      <c r="BC19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>40</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BF19" t="n">
-        <v>2.62</v>
+        <v>16.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.43</v>
       </c>
-      <c r="G20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>1.05</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,378 +4623,2124 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.68</v>
+        <v>2.82</v>
       </c>
       <c r="G22" t="n">
-        <v>1.87</v>
+        <v>3.05</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="J22" t="n">
-        <v>1.09</v>
+        <v>2.64</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>2.88</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>2.12</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="U22" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>2.14</v>
+        <v>1.48</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>24</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BA22" t="n">
-        <v>1.53</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.53</v>
+        <v>8.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Al Ittihad (EGY)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Forest Green</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Tondela</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>290</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>520</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X31" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Internacional de Palmira</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Quindio</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F32" t="n">
         <v>1.99</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G32" t="n">
         <v>2.24</v>
       </c>
-      <c r="H23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I32" t="n">
         <v>5.8</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J32" t="n">
         <v>2.78</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K32" t="n">
         <v>3.5</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L32" t="n">
         <v>1.46</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M32" t="n">
         <v>1.11</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="N32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O32" t="n">
         <v>1.5</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P32" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="Q32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.19</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="S32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V32" t="n">
         <v>1.21</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="W32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X32" t="n">
         <v>11</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y32" t="n">
         <v>15</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z32" t="n">
         <v>40</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA32" t="n">
         <v>150</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB32" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC32" t="n">
         <v>9</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD32" t="n">
         <v>24</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE32" t="n">
         <v>100</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AF32" t="n">
         <v>14</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AG32" t="n">
         <v>14</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH32" t="n">
         <v>29</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AI32" t="n">
         <v>120</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AJ32" t="n">
         <v>34</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AK32" t="n">
         <v>36</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AL32" t="n">
         <v>70</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AM32" t="n">
         <v>230</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AN32" t="n">
         <v>32</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AO32" t="n">
         <v>150</v>
       </c>
-      <c r="AP23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR23" t="n">
+      <c r="AP32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR32" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AS32" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT23" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="AT32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW32" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA23" t="n">
+      <c r="AX32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA32" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD23" t="n">
+      <c r="BB32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD32" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BE32" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG23" t="n">
+      <c r="BF32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG32" t="n">
         <v>4.2</v>
       </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-04-28 07:30:14</t>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -781,22 +781,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>1.51</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>1.05</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I3" t="n">
         <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
@@ -984,13 +984,13 @@
         <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.96</v>
@@ -1005,10 +1005,10 @@
         <v>1.74</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>38</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1029,10 +1029,10 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>25</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BF3" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.41</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1593,10 +1593,10 @@
         <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB6" t="n">
         <v>19</v>
@@ -1608,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF6" t="n">
         <v>36</v>
@@ -1665,38 +1665,38 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD6" t="n">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
         <v>9.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="I7" t="n">
         <v>2.44</v>
@@ -1742,7 +1742,7 @@
         <v>2.78</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,7 +1754,7 @@
         <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
         <v>1.35</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
         <v>1.87</v>
@@ -1933,7 +1933,7 @@
         <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -1951,7 +1951,7 @@
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
         <v>1.99</v>
@@ -1960,7 +1960,7 @@
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1978,7 +1978,7 @@
         <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
         <v>60</v>
@@ -1987,34 +1987,34 @@
         <v>230</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE8" t="n">
         <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>130</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
@@ -2029,62 +2029,62 @@
         <v>200</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2145,10 +2145,10 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
@@ -2160,7 +2160,7 @@
         <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
         <v>1.55</v>
@@ -2232,7 +2232,7 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2256,10 +2256,10 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB9" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
         <v>5.1</v>
@@ -2274,11 +2274,11 @@
         <v>5</v>
       </c>
       <c r="BG9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="G10" t="n">
         <v>2.44</v>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.02</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2503,40 +2503,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="I11" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
         <v>1.59</v>
@@ -2545,28 +2545,28 @@
         <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
         <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AB11" t="n">
         <v>30</v>
@@ -2581,10 +2581,10 @@
         <v>970</v>
       </c>
       <c r="AF11" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AG11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2593,28 +2593,28 @@
         <v>30</v>
       </c>
       <c r="AJ11" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AK11" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM11" t="n">
         <v>85</v>
       </c>
-      <c r="AM11" t="n">
-        <v>110</v>
-      </c>
       <c r="AN11" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
         <v>9.199999999999999</v>
@@ -2626,47 +2626,47 @@
         <v>21</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AW11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY11" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
         <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -2739,16 +2739,16 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
         <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AV12" t="n">
         <v>1.48</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="BF12" t="n">
-        <v>9</v>
+        <v>1.96</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.01</v>
@@ -2924,7 +2924,7 @@
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3118,7 +3118,7 @@
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
         <v>1.12</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>NK Jadran Dekani</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>NK Brinje Grosuplje</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>1.52</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>6.4</v>
+        <v>1.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>1.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="H16" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>2.92</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z16" t="n">
         <v>13</v>
       </c>
-      <c r="Y16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>18</v>
-      </c>
       <c r="AA16" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="AC16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX16" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AY16" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H17" t="n">
         <v>2.34</v>
       </c>
-      <c r="H17" t="n">
-        <v>3.55</v>
-      </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.45</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
         <v>4.1</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH17" t="n">
         <v>22</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>25</v>
-      </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.99</v>
+        <v>4.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU17" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AV17" t="n">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.99</v>
+        <v>5.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.92</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.99</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.99</v>
+        <v>18.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G18" t="n">
         <v>3.2</v>
@@ -3870,7 +3870,7 @@
         <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
@@ -3903,16 +3903,16 @@
         <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
         <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
         <v>19</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="H20" t="n">
-        <v>2.22</v>
+        <v>2.98</v>
       </c>
       <c r="I20" t="n">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.29</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U20" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
         <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>2.08</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>2.08</v>
       </c>
       <c r="AX20" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>2.08</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>2.08</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>2.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.9</v>
+        <v>2.08</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="I21" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="T21" t="n">
         <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="W21" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
         <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
         <v>970</v>
       </c>
       <c r="AH21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO21" t="n">
         <v>970</v>
       </c>
-      <c r="AI21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>24</v>
-      </c>
       <c r="AP21" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,184 +4623,184 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I22" t="n">
         <v>3.05</v>
       </c>
-      <c r="H22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.55</v>
-      </c>
       <c r="J22" t="n">
-        <v>2.64</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.12</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>2.98</v>
       </c>
       <c r="T22" t="n">
-        <v>2.52</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA22" t="n">
         <v>6</v>
       </c>
-      <c r="Y22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP22" t="n">
+      <c r="BB22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF22" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG22" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="J23" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="K23" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="L23" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O23" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="P23" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT23" t="n">
         <v>6.2</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,73 +5016,73 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.99</v>
+        <v>2.34</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="I24" t="n">
         <v>4.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>2.76</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="U24" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W24" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5091,25 +5091,25 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5118,84 +5118,84 @@
         <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>40</v>
+        <v>5.1</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF24" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="H25" t="n">
         <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="R25" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="U25" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="X25" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
         <v>22</v>
       </c>
-      <c r="Z25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AL25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
         <v>14</v>
       </c>
-      <c r="AC25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>15</v>
       </c>
-      <c r="AG25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK25" t="n">
+      <c r="BA25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC25" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>8.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G26" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P26" t="n">
         <v>2.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R26" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S26" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y26" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Z26" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB26" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AC26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF26" t="n">
         <v>15</v>
       </c>
-      <c r="AD26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG26" t="n">
         <v>21</v>
       </c>
-      <c r="AG26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>2.34</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.05</v>
+        <v>1.87</v>
       </c>
       <c r="G27" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="H27" t="n">
-        <v>2.66</v>
+        <v>3.7</v>
       </c>
       <c r="I27" t="n">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BC27" t="n">
         <v>2.36</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>34</v>
-      </c>
       <c r="BD27" t="n">
-        <v>50</v>
+        <v>2.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>110</v>
+        <v>2.48</v>
       </c>
       <c r="BF27" t="n">
-        <v>40</v>
+        <v>2.14</v>
       </c>
       <c r="BG27" t="n">
-        <v>30</v>
+        <v>2.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.13</v>
+        <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="H28" t="n">
-        <v>25</v>
+        <v>2.66</v>
       </c>
       <c r="I28" t="n">
-        <v>30</v>
+        <v>2.68</v>
       </c>
       <c r="J28" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD28" t="n">
         <v>12.5</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N28" t="n">
-        <v>8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="AE28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI28" t="n">
         <v>55</v>
       </c>
-      <c r="Y28" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>290</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>95</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>520</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AJ28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL28" t="n">
         <v>60</v>
       </c>
-      <c r="AI28" t="n">
-        <v>330</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>46</v>
-      </c>
       <c r="AM28" t="n">
-        <v>330</v>
+        <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.82</v>
+        <v>42</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP28" t="n">
         <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>11</v>
-      </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.4</v>
+        <v>48</v>
       </c>
       <c r="BC28" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BD28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BE28" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.58</v>
+        <v>40</v>
       </c>
       <c r="BG28" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.15</v>
       </c>
       <c r="H29" t="n">
-        <v>1.09</v>
+        <v>24</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>1.09</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>1.24</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R29" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="S29" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -6237,10 +6237,10 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,184 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.78</v>
+        <v>1.24</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.02</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.18</v>
-      </c>
       <c r="X31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -6563,184 +6563,378 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="G32" t="n">
-        <v>2.24</v>
+        <v>1.84</v>
       </c>
       <c r="H32" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="J32" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="L32" t="n">
         <v>1.46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="O32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V32" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W32" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y32" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z32" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA32" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC32" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD32" t="n">
         <v>24</v>
       </c>
       <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:47:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE33" t="n">
         <v>100</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AF33" t="n">
         <v>14</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AG33" t="n">
         <v>14</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AH33" t="n">
         <v>29</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AI33" t="n">
         <v>120</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AJ33" t="n">
         <v>34</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AK33" t="n">
         <v>36</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AL33" t="n">
         <v>70</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AM33" t="n">
         <v>230</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AN33" t="n">
         <v>32</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AO33" t="n">
         <v>150</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AP33" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AQ33" t="n">
         <v>9</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AR33" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AS33" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AT33" t="n">
         <v>5.2</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AU33" t="n">
         <v>5.6</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AV33" t="n">
         <v>14</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AW33" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AX33" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AY33" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="AZ33" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BA33" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB33" t="n">
         <v>19.5</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BC33" t="n">
         <v>20</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BD33" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BE33" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BF33" t="n">
         <v>19</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BG33" t="n">
         <v>4.2</v>
       </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-04-28 09:38:52</t>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
         <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
@@ -1002,7 +1002,7 @@
         <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1071,10 +1071,10 @@
         <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV3" t="n">
         <v>4.1</v>
@@ -1104,7 +1104,7 @@
         <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
         <v>4.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O4" t="n">
         <v>1.52</v>
@@ -1178,19 +1178,19 @@
         <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
         <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
         <v>1.72</v>
@@ -1638,7 +1638,7 @@
         <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY6" t="n">
         <v>15.5</v>
@@ -1674,19 +1674,19 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
         <v>6.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -1960,7 +1960,7 @@
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1987,7 +1987,7 @@
         <v>230</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -2029,7 +2029,7 @@
         <v>200</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>3.65</v>
@@ -2041,16 +2041,16 @@
         <v>4.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AV8" t="n">
         <v>3.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
         <v>3.2</v>
@@ -2059,16 +2059,16 @@
         <v>3.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
         <v>3.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BD8" t="n">
         <v>4.1</v>
@@ -2077,14 +2077,14 @@
         <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BG8" t="n">
         <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2.46</v>
       </c>
       <c r="I9" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
@@ -2133,7 +2133,7 @@
         <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2145,10 +2145,10 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
@@ -2157,13 +2157,13 @@
         <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
         <v>1.07</v>
       </c>
       <c r="S10" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>1.52</v>
       </c>
       <c r="I11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
@@ -2527,7 +2527,7 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
@@ -2545,13 +2545,13 @@
         <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -2560,19 +2560,19 @@
         <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
         <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
         <v>11</v>
@@ -2584,10 +2584,10 @@
         <v>55</v>
       </c>
       <c r="AG11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>30</v>
@@ -2608,16 +2608,16 @@
         <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS11" t="n">
         <v>12</v>
@@ -2629,44 +2629,44 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AZ11" t="n">
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
         <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
         <v>1.57</v>
@@ -2724,7 +2724,7 @@
         <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P12" t="n">
         <v>1.44</v>
@@ -2748,7 +2748,7 @@
         <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -3476,22 +3476,22 @@
         <v>6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H16" t="n">
         <v>1.46</v>
       </c>
       <c r="I16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -3512,16 +3512,16 @@
         <v>1.75</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U16" t="n">
         <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="W16" t="n">
         <v>1.15</v>
@@ -3533,7 +3533,7 @@
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AA16" t="n">
         <v>970</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3575,25 +3575,25 @@
         <v>75</v>
       </c>
       <c r="AN16" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
         <v>9.4</v>
@@ -3602,41 +3602,41 @@
         <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
         <v>8.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
         <v>4.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -3667,34 +3667,34 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="G17" t="n">
         <v>3.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
         <v>1.71</v>
@@ -3712,7 +3712,7 @@
         <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V17" t="n">
         <v>1.67</v>
@@ -3724,7 +3724,7 @@
         <v>12.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z17" t="n">
         <v>16.5</v>
@@ -3733,58 +3733,58 @@
         <v>38</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
         <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR17" t="n">
         <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
@@ -3793,44 +3793,44 @@
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
         <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BG17" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -3861,61 +3861,61 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
         <v>1.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
         <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
         <v>1.46</v>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
         <v>14.5</v>
@@ -3930,10 +3930,10 @@
         <v>15.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
         <v>34</v>
@@ -3948,13 +3948,13 @@
         <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ18" t="n">
         <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
         <v>50</v>
@@ -3966,7 +3966,7 @@
         <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP18" t="n">
         <v>11.5</v>
@@ -3978,7 +3978,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -4002,10 +4002,10 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BC18" t="n">
         <v>4.3</v>
@@ -4014,17 +4014,17 @@
         <v>4.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G19" t="n">
         <v>2.6</v>
@@ -4088,13 +4088,13 @@
         <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.7</v>
@@ -4172,7 +4172,7 @@
         <v>18.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -4249,64 +4249,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="H20" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
         <v>1.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
         <v>2.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4315,22 +4315,22 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
         <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
         <v>24</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AQ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AW20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AX20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AZ20" t="n">
         <v>10.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
         <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I21" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.29</v>
@@ -4491,10 +4491,10 @@
         <v>2.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -4575,7 +4575,7 @@
         <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
@@ -4602,11 +4602,11 @@
         <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G22" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H22" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -4661,34 +4661,34 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
         <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
         <v>970</v>
@@ -4697,7 +4697,7 @@
         <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
         <v>48</v>
@@ -4745,19 +4745,19 @@
         <v>23</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AR22" t="n">
         <v>5.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AU22" t="n">
         <v>4</v>
@@ -4766,13 +4766,13 @@
         <v>4.7</v>
       </c>
       <c r="AW22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX22" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX22" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AY22" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>5</v>
@@ -4784,23 +4784,23 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE22" t="n">
         <v>6.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G23" t="n">
         <v>3.05</v>
@@ -4942,7 +4942,7 @@
         <v>5.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR23" t="n">
         <v>15.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
         <v>2.76</v>
       </c>
       <c r="K24" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L24" t="n">
         <v>1.54</v>
@@ -5064,7 +5064,7 @@
         <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T24" t="n">
         <v>2.26</v>
@@ -5073,7 +5073,7 @@
         <v>1.65</v>
       </c>
       <c r="V24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
         <v>1.62</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
         <v>3.65</v>
@@ -5237,7 +5237,7 @@
         <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -5288,13 +5288,13 @@
         <v>10</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
         <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF25" t="n">
         <v>13.5</v>
@@ -5309,13 +5309,13 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK25" t="n">
         <v>22</v>
       </c>
       <c r="AL25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5333,10 +5333,10 @@
         <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
@@ -5369,7 +5369,7 @@
         <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE25" t="n">
         <v>9.4</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G26" t="n">
         <v>1.95</v>
       </c>
       <c r="H26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>4.4</v>
@@ -5431,7 +5431,7 @@
         <v>4.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
@@ -5461,7 +5461,7 @@
         <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
         <v>2.04</v>
@@ -5566,7 +5566,7 @@
         <v>8.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
         <v>7.4</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I27" t="n">
         <v>4.2</v>
@@ -5622,7 +5622,7 @@
         <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.2</v>
@@ -5658,7 +5658,7 @@
         <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H28" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I28" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J28" t="n">
         <v>3.3</v>
@@ -5819,64 +5819,64 @@
         <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R28" t="n">
         <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X28" t="n">
         <v>10.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
         <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF28" t="n">
         <v>18.5</v>
@@ -5888,13 +5888,13 @@
         <v>20</v>
       </c>
       <c r="AI28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>55</v>
       </c>
-      <c r="AJ28" t="n">
-        <v>50</v>
-      </c>
       <c r="AK28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL28" t="n">
         <v>60</v>
@@ -5903,7 +5903,7 @@
         <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO28" t="n">
         <v>32</v>
@@ -5912,16 +5912,16 @@
         <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS28" t="n">
         <v>36</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6.8</v>
@@ -5939,16 +5939,16 @@
         <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB28" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC28" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD28" t="n">
         <v>50</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -6001,13 +6001,13 @@
         <v>1.15</v>
       </c>
       <c r="H29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="K29" t="n">
         <v>11.5</v>
@@ -6019,10 +6019,10 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P29" t="n">
         <v>3.3</v>
@@ -6031,19 +6031,19 @@
         <v>1.39</v>
       </c>
       <c r="R29" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T29" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
         <v>7.6</v>
@@ -6052,67 +6052,67 @@
         <v>55</v>
       </c>
       <c r="Y29" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Z29" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD29" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AE29" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AF29" t="n">
         <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH29" t="n">
         <v>55</v>
       </c>
       <c r="AI29" t="n">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AJ29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM29" t="n">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
         <v>10.5</v>
@@ -6121,44 +6121,44 @@
         <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX29" t="n">
         <v>7.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BA29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB29" t="n">
         <v>7.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BG29" t="n">
         <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -6213,13 +6213,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O30" t="n">
         <v>1.01</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Q30" t="n">
         <v>1.01</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,184 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M31" t="n">
         <v>1.09</v>
       </c>
-      <c r="K31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N31" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -6563,378 +6563,184 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N32" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P32" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.04</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="X32" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB32" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC32" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF32" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AK32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL32" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN32" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB32" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV32" t="n">
+      <c r="BC32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE32" t="n">
         <v>5</v>
       </c>
-      <c r="AW32" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB32" t="n">
+      <c r="BF32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG32" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Internacional de Palmira</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="X33" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
         <v>4.9</v>
@@ -778,25 +778,25 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="P2" t="n">
         <v>1.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -808,28 +808,28 @@
         <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -838,10 +838,10 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -868,22 +868,22 @@
         <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
         <v>1.03</v>
@@ -892,10 +892,10 @@
         <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
@@ -1002,7 +1002,7 @@
         <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1071,10 +1071,10 @@
         <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AV3" t="n">
         <v>4.1</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
         <v>3.3</v>
@@ -1166,31 +1166,31 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
@@ -1199,116 +1199,116 @@
         <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>1.82</v>
       </c>
       <c r="I6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
@@ -1581,7 +1581,7 @@
         <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.26</v>
@@ -1674,7 +1674,7 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
         <v>7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
         <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
         <v>1.35</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -1945,7 +1945,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -1954,7 +1954,7 @@
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
@@ -1969,10 +1969,10 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2014,7 +2014,7 @@
         <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
@@ -2029,62 +2029,62 @@
         <v>200</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AW8" t="n">
         <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AY8" t="n">
         <v>3.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BC8" t="n">
         <v>3.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>2.46</v>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
@@ -2133,7 +2133,7 @@
         <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2145,10 +2145,10 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
@@ -2157,13 +2157,13 @@
         <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -2697,40 +2697,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J12" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="K12" t="n">
         <v>3.15</v>
       </c>
       <c r="L12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="P12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.15</v>
@@ -2739,22 +2739,22 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.48</v>
+        <v>6.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -3482,13 +3482,13 @@
         <v>1.46</v>
       </c>
       <c r="I16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.2</v>
@@ -3521,7 +3521,7 @@
         <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="W16" t="n">
         <v>1.15</v>
@@ -3557,7 +3557,7 @@
         <v>27</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3566,7 +3566,7 @@
         <v>170</v>
       </c>
       <c r="AK16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="n">
         <v>65</v>
@@ -3581,19 +3581,19 @@
         <v>5.2</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU16" t="n">
         <v>9.4</v>
@@ -3605,38 +3605,38 @@
         <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC16" t="n">
         <v>9</v>
       </c>
-      <c r="BC16" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
         <v>4.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H17" t="n">
         <v>2.38</v>
@@ -3715,10 +3715,10 @@
         <v>1.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X17" t="n">
         <v>12.5</v>
@@ -3769,13 +3769,13 @@
         <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO17" t="n">
         <v>29</v>
       </c>
       <c r="AP17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
         <v>8</v>
@@ -3808,10 +3808,10 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
         <v>7.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="I18" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.31</v>
@@ -3885,7 +3885,7 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
@@ -3894,7 +3894,7 @@
         <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
         <v>1.38</v>
@@ -3903,40 +3903,40 @@
         <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB18" t="n">
         <v>15.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>25</v>
@@ -3948,7 +3948,7 @@
         <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ18" t="n">
         <v>55</v>
@@ -3966,7 +3966,7 @@
         <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>11.5</v>
@@ -3978,7 +3978,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT18" t="n">
         <v>10.5</v>
@@ -3990,10 +3990,10 @@
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AY18" t="n">
         <v>11</v>
@@ -4002,19 +4002,19 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.3</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF18" t="n">
         <v>18.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
         <v>2.6</v>
@@ -4073,13 +4073,13 @@
         <v>3.65</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>1.29</v>
@@ -4088,7 +4088,7 @@
         <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
@@ -4211,14 +4211,14 @@
         <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
         <v>22</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H20" t="n">
         <v>3.3</v>
@@ -4261,7 +4261,7 @@
         <v>3.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
         <v>3.8</v>
@@ -4276,7 +4276,7 @@
         <v>3.95</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P20" t="n">
         <v>1.99</v>
@@ -4285,10 +4285,10 @@
         <v>1.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="T20" t="n">
         <v>1.68</v>
@@ -4300,119 +4300,119 @@
         <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
         <v>21</v>
       </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>15</v>
-      </c>
       <c r="AS20" t="n">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.06</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE20" t="n">
         <v>7</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BF20" t="n">
-        <v>2.06</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.06</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G21" t="n">
         <v>3.4</v>
@@ -4452,7 +4452,7 @@
         <v>2.24</v>
       </c>
       <c r="I21" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
@@ -4491,7 +4491,7 @@
         <v>2.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W21" t="n">
         <v>1.41</v>
@@ -4551,7 +4551,7 @@
         <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
@@ -4575,19 +4575,19 @@
         <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA21" t="n">
         <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4596,17 +4596,17 @@
         <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H22" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -4667,10 +4667,10 @@
         <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
@@ -4685,10 +4685,10 @@
         <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
         <v>970</v>
@@ -4751,7 +4751,7 @@
         <v>4.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS22" t="n">
         <v>6.2</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -4837,16 +4837,16 @@
         <v>3.05</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I23" t="n">
         <v>3.55</v>
       </c>
       <c r="J23" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="K23" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="L23" t="n">
         <v>1.67</v>
@@ -4855,25 +4855,25 @@
         <v>1.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="O23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="P23" t="n">
         <v>1.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
         <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
         <v>1.57</v>
@@ -4888,10 +4888,10 @@
         <v>6</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA23" t="n">
         <v>80</v>
@@ -4900,10 +4900,10 @@
         <v>7</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>75</v>
@@ -4939,16 +4939,16 @@
         <v>120</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR23" t="n">
         <v>15.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT23" t="n">
         <v>6.2</v>
@@ -4960,7 +4960,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AX23" t="n">
         <v>14.5</v>
@@ -4972,29 +4972,29 @@
         <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
         <v>2.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>2.76</v>
@@ -5064,7 +5064,7 @@
         <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T24" t="n">
         <v>2.26</v>
@@ -5073,7 +5073,7 @@
         <v>1.65</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W24" t="n">
         <v>1.62</v>
@@ -5160,7 +5160,7 @@
         <v>11.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>4.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I25" t="n">
         <v>4.2</v>
@@ -5264,7 +5264,7 @@
         <v>1.77</v>
       </c>
       <c r="U25" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V25" t="n">
         <v>1.31</v>
@@ -5276,7 +5276,7 @@
         <v>15.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>10</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD25" t="n">
         <v>16.5</v>
@@ -5312,10 +5312,10 @@
         <v>24</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5333,10 +5333,10 @@
         <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
@@ -5360,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>21</v>
@@ -5369,10 +5369,10 @@
         <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BF25" t="n">
         <v>12</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>1.87</v>
       </c>
       <c r="G26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
         <v>4.1</v>
@@ -5443,7 +5443,7 @@
         <v>1.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q26" t="n">
         <v>1.58</v>
@@ -5461,10 +5461,10 @@
         <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X26" t="n">
         <v>26</v>
@@ -5476,7 +5476,7 @@
         <v>36</v>
       </c>
       <c r="AA26" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="n">
         <v>14</v>
@@ -5572,11 +5572,11 @@
         <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="H27" t="n">
         <v>3.65</v>
@@ -5631,7 +5631,7 @@
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
         <v>1.19</v>
@@ -5643,10 +5643,10 @@
         <v>1.57</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="S27" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="T27" t="n">
         <v>1.4</v>
@@ -5658,13 +5658,13 @@
         <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z27" t="n">
         <v>48</v>
@@ -5673,104 +5673,104 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.48</v>
+        <v>6.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.28</v>
+        <v>5.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.34</v>
+        <v>5.7</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="AX27" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>2.22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.32</v>
+        <v>5.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.48</v>
+        <v>7.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.38</v>
+        <v>6.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.36</v>
+        <v>5.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.14</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -5807,10 +5807,10 @@
         <v>3.2</v>
       </c>
       <c r="H28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I28" t="n">
         <v>2.62</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.64</v>
       </c>
       <c r="J28" t="n">
         <v>3.3</v>
@@ -5819,40 +5819,40 @@
         <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
         <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
         <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X28" t="n">
         <v>10.5</v>
@@ -5861,10 +5861,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB28" t="n">
         <v>10.5</v>
@@ -5879,10 +5879,10 @@
         <v>30</v>
       </c>
       <c r="AF28" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH28" t="n">
         <v>20</v>
@@ -5894,7 +5894,7 @@
         <v>55</v>
       </c>
       <c r="AK28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL28" t="n">
         <v>60</v>
@@ -5906,16 +5906,16 @@
         <v>44</v>
       </c>
       <c r="AO28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
         <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS28" t="n">
         <v>36</v>
@@ -5933,13 +5933,13 @@
         <v>29</v>
       </c>
       <c r="AX28" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
         <v>46</v>
@@ -5960,11 +5960,11 @@
         <v>40</v>
       </c>
       <c r="BG28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -6019,28 +6019,28 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P29" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="R29" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="S29" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U29" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
         <v>1.04</v>
@@ -6055,110 +6055,110 @@
         <v>90</v>
       </c>
       <c r="Z29" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>490</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR29" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC29" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>95</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>440</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>550</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AS29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>10.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BA29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC29" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD29" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="BG29" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         <v>6.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K31" t="n">
         <v>4.9</v>
@@ -6431,7 +6431,7 @@
         <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W31" t="n">
         <v>2.16</v>
@@ -6491,256 +6491,450 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.94</v>
+        <v>1.97</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.96</v>
+        <v>1.74</v>
       </c>
       <c r="AT31" t="n">
         <v>3.65</v>
       </c>
       <c r="AU31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.5</v>
+        <v>1.89</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="AX31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY31" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY31" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="BB31" t="n">
-        <v>3.5</v>
+        <v>1.87</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.55</v>
+        <v>1.89</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.94</v>
+        <v>1.97</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.96</v>
+        <v>1.73</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.98</v>
+        <v>2.02</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CA Rentistas</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Internacional de Palmira</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Quindio</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G33" t="n">
         <v>2.22</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H33" t="n">
         <v>4.2</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>5.2</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>2.84</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>3.5</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L33" t="n">
         <v>1.46</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M33" t="n">
         <v>1.11</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N33" t="n">
         <v>2.62</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O33" t="n">
         <v>1.5</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P33" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>2.26</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
         <v>4.5</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>2.1</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>1.74</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V33" t="n">
         <v>1.24</v>
       </c>
-      <c r="W32" t="n">
+      <c r="W33" t="n">
         <v>1.82</v>
       </c>
-      <c r="X32" t="n">
+      <c r="X33" t="n">
         <v>11</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y33" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="Z33" t="n">
         <v>40</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AA33" t="n">
         <v>150</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AB33" t="n">
         <v>8</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AC33" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AD33" t="n">
         <v>21</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AE33" t="n">
         <v>100</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AF33" t="n">
         <v>14</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AG33" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AH33" t="n">
         <v>29</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AI33" t="n">
         <v>120</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AJ33" t="n">
         <v>29</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AK33" t="n">
         <v>30</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AL33" t="n">
         <v>70</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AM33" t="n">
         <v>230</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AN33" t="n">
         <v>28</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AO33" t="n">
         <v>150</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AP33" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AQ33" t="n">
         <v>10</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AR33" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AS33" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AT33" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AU33" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AV33" t="n">
         <v>14</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AW33" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AX33" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AY33" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="AZ33" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BA33" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB33" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BC33" t="n">
         <v>20</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BD33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BE33" t="n">
         <v>5</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BF33" t="n">
         <v>4.3</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BG33" t="n">
         <v>4.9</v>
       </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-04-28 13:56:30</t>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,61 +757,61 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O2" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
@@ -820,7 +820,7 @@
         <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -832,25 +832,25 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
         <v>2.68</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
         <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1011,7 +1011,7 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1044,7 +1044,7 @@
         <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
@@ -1053,22 +1053,22 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
         <v>3.2</v>
@@ -1077,44 +1077,44 @@
         <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AY3" t="n">
         <v>3.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC3" t="n">
         <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
         <v>4.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1157,40 +1157,40 @@
         <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
         <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
@@ -1217,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
         <v>55</v>
@@ -1253,62 +1253,62 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AR4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4</v>
-      </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
         <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
         <v>1.72</v>
@@ -1635,7 +1635,7 @@
         <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO6" t="n">
         <v>13</v>
@@ -1665,7 +1665,7 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
         <v>15.5</v>
@@ -1677,16 +1677,16 @@
         <v>6.6</v>
       </c>
       <c r="BB6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
         <v>6.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>1.91</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
         <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -1945,7 +1945,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -1954,7 +1954,7 @@
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
         <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="I9" t="n">
         <v>2.82</v>
@@ -2130,10 +2130,10 @@
         <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2145,10 +2145,10 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
@@ -2157,10 +2157,10 @@
         <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
         <v>1.55</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>2.66</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>7</v>
@@ -2512,13 +2512,13 @@
         <v>1.52</v>
       </c>
       <c r="I11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.26</v>
@@ -2551,7 +2551,7 @@
         <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
         <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="n">
         <v>2.76</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="L12" t="n">
         <v>1.56</v>
@@ -2730,7 +2730,7 @@
         <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R12" t="n">
         <v>1.15</v>
@@ -2751,7 +2751,7 @@
         <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y12" t="n">
         <v>13.5</v>
@@ -2811,10 +2811,10 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AT12" t="n">
         <v>5.1</v>
@@ -2823,44 +2823,44 @@
         <v>4.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2924,13 +2924,13 @@
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>1.12</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="G16" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="I16" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
         <v>34</v>
@@ -3533,10 +3533,10 @@
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AB16" t="n">
         <v>36</v>
@@ -3548,16 +3548,16 @@
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AF16" t="n">
         <v>65</v>
       </c>
       <c r="AG16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3569,74 +3569,74 @@
         <v>75</v>
       </c>
       <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN16" t="n">
         <v>65</v>
       </c>
-      <c r="AM16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>60</v>
-      </c>
       <c r="AO16" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AW16" t="n">
         <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>2.38</v>
       </c>
       <c r="I17" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -3685,7 +3685,7 @@
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -3709,13 +3709,13 @@
         <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
         <v>1.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W17" t="n">
         <v>1.37</v>
@@ -3808,16 +3808,16 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC17" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
         <v>8</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H18" t="n">
         <v>3.3</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.38</v>
-      </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
         <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR18" t="n">
         <v>21</v>
       </c>
-      <c r="AA18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>15</v>
-      </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.5</v>
+        <v>36</v>
       </c>
       <c r="BB18" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,34 +4046,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I19" t="n">
         <v>2.6</v>
       </c>
-      <c r="H19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -4082,150 +4082,150 @@
         <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF19" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI19" t="n">
         <v>44</v>
       </c>
       <c r="AJ19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK19" t="n">
         <v>38</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS19" t="n">
         <v>27</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>28</v>
+        <v>4.5</v>
       </c>
       <c r="AX19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>15</v>
       </c>
-      <c r="AY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>22</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.7</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1.29</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL20" t="n">
         <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA20" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>36</v>
-      </c>
       <c r="BB20" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
-        <v>25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H21" t="n">
         <v>2.24</v>
       </c>
       <c r="I21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
@@ -4506,7 +4506,7 @@
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
@@ -4566,7 +4566,7 @@
         <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
         <v>10</v>
@@ -4581,7 +4581,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA21" t="n">
         <v>7.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="U22" t="n">
         <v>2.3</v>
@@ -4745,7 +4745,7 @@
         <v>23</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>4.6</v>
@@ -4769,7 +4769,7 @@
         <v>5.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -4793,21 +4793,21 @@
         <v>6.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BG22" t="n">
         <v>5.3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,184 +4817,184 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.88</v>
+        <v>1.51</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.86</v>
+        <v>7.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="O23" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="P23" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>2.16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="S23" t="n">
-        <v>8.6</v>
+        <v>2.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="G24" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="K24" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="L24" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="O24" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X24" t="n">
         <v>6</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA24" t="n">
         <v>7.6</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="BB24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD24" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE24" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BF24" t="n">
         <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.65</v>
+        <v>2.76</v>
       </c>
       <c r="K25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT25" t="n">
         <v>3.9</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>9</v>
-      </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>40</v>
+        <v>5.1</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="BF25" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1.87</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.58</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
         <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="X26" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN26" t="n">
         <v>14</v>
       </c>
-      <c r="AC26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS26" t="n">
         <v>15</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX26" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>12.5</v>
       </c>
       <c r="AY26" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC26" t="n">
         <v>18.5</v>
       </c>
-      <c r="BC26" t="n">
-        <v>15</v>
-      </c>
       <c r="BD26" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.92</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.95</v>
-      </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J27" t="n">
         <v>4.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4</v>
       </c>
       <c r="K27" t="n">
         <v>4.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S27" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T27" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y27" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z27" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ27" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="BA27" t="n">
         <v>7.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BE27" t="n">
         <v>7.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="G28" t="n">
-        <v>3.2</v>
+        <v>1.99</v>
       </c>
       <c r="H28" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="I28" t="n">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="P28" t="n">
-        <v>1.74</v>
+        <v>2.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="U28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W28" t="n">
         <v>2</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.45</v>
-      </c>
       <c r="X28" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA28" t="n">
         <v>7</v>
       </c>
-      <c r="AD28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>46</v>
-      </c>
       <c r="BB28" t="n">
-        <v>50</v>
+        <v>6.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>36</v>
+        <v>5.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>50</v>
+        <v>6.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>100</v>
+        <v>7.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>1.15</v>
+        <v>3.15</v>
       </c>
       <c r="H29" t="n">
-        <v>23</v>
+        <v>2.58</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB29" t="n">
         <v>10.5</v>
       </c>
-      <c r="K29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="X29" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>320</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>14</v>
-      </c>
       <c r="AC29" t="n">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>400</v>
+        <v>29</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.6</v>
+        <v>19.5</v>
       </c>
       <c r="AG29" t="n">
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="AI29" t="n">
-        <v>260</v>
+        <v>46</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="AK29" t="n">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AL29" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.76</v>
+        <v>44</v>
       </c>
       <c r="AO29" t="n">
-        <v>490</v>
+        <v>29</v>
       </c>
       <c r="AP29" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AT29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
         <v>11.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BC29" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BD29" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BE29" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.54</v>
+        <v>40</v>
       </c>
       <c r="BG29" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>1.16</v>
       </c>
       <c r="H30" t="n">
-        <v>1.09</v>
+        <v>25</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>1.23</v>
+        <v>8.4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="P30" t="n">
-        <v>1.23</v>
+        <v>3.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R30" t="n">
-        <v>1.13</v>
+        <v>2.04</v>
       </c>
       <c r="S30" t="n">
-        <v>1.05</v>
+        <v>1.92</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="G31" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>1.09</v>
       </c>
       <c r="I31" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.84</v>
+        <v>1.23</v>
       </c>
       <c r="O31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V31" t="n">
         <v>1.4</v>
       </c>
-      <c r="P31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.19</v>
-      </c>
       <c r="W31" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,378 +6563,572 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="G32" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="H32" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K32" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="O32" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>1.94</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CA Rentistas</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Internacional de Palmira</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Quindio</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G34" t="n">
         <v>2.22</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H34" t="n">
         <v>4.2</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>5.2</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>2.84</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>3.5</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L34" t="n">
         <v>1.46</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>1.11</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>2.62</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O34" t="n">
         <v>1.5</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P34" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>2.26</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>1.2</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>4.5</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>2.1</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>1.74</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V34" t="n">
         <v>1.24</v>
       </c>
-      <c r="W33" t="n">
+      <c r="W34" t="n">
         <v>1.82</v>
       </c>
-      <c r="X33" t="n">
+      <c r="X34" t="n">
         <v>11</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Y34" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="Z34" t="n">
         <v>40</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AA34" t="n">
         <v>150</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AB34" t="n">
         <v>8</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AC34" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AD34" t="n">
         <v>21</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AE34" t="n">
         <v>100</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AF34" t="n">
         <v>14</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AG34" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AH34" t="n">
         <v>29</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AI34" t="n">
         <v>120</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AJ34" t="n">
         <v>29</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AK34" t="n">
         <v>30</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AL34" t="n">
         <v>70</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AM34" t="n">
         <v>230</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AN34" t="n">
         <v>28</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AO34" t="n">
         <v>150</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AP34" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AQ34" t="n">
         <v>10</v>
       </c>
-      <c r="AR33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS33" t="n">
+      <c r="AR34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS34" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AT34" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AU34" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AV34" t="n">
         <v>14</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AW34" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AX34" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AY34" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="AZ34" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BA34" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC33" t="n">
+      <c r="BB34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC34" t="n">
         <v>20</v>
       </c>
-      <c r="BD33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE33" t="n">
+      <c r="BD34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE34" t="n">
         <v>5</v>
       </c>
-      <c r="BF33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG33" t="n">
+      <c r="BF34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG34" t="n">
         <v>4.9</v>
       </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-04-28 16:05:14</t>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -757,31 +757,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
@@ -790,25 +790,25 @@
         <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -835,13 +835,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
@@ -850,7 +850,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -859,68 +859,68 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.95</v>
+        <v>1.93</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>1.84</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>1.93</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>1.93</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>1.87</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.05</v>
+        <v>1.87</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>1.82</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
@@ -969,7 +969,7 @@
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -990,19 +990,19 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1062,59 +1062,59 @@
         <v>3.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU3" t="n">
         <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY3" t="n">
         <v>3.7</v>
       </c>
-      <c r="AY3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.62</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
         <v>2.96</v>
@@ -1184,13 +1184,13 @@
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
@@ -1205,7 +1205,7 @@
         <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
         <v>70</v>
@@ -1229,7 +1229,7 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>85</v>
@@ -1298,7 +1298,7 @@
         <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
         <v>5.3</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
         <v>4.9</v>
@@ -1542,10 +1542,10 @@
         <v>1.82</v>
       </c>
       <c r="I6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
         <v>4.3</v>
@@ -1566,7 +1566,7 @@
         <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
@@ -1575,37 +1575,37 @@
         <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W6" t="n">
         <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
         <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE6" t="n">
         <v>19.5</v>
@@ -1641,10 +1641,10 @@
         <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>11</v>
@@ -1656,7 +1656,7 @@
         <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>9.199999999999999</v>
@@ -1665,38 +1665,38 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="n">
         <v>9.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
         <v>2.42</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.01</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
         <v>5.3</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1945,7 +1945,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -1954,13 +1954,13 @@
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1969,10 +1969,10 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2056,7 +2056,7 @@
         <v>3.15</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>3.75</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
         <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.39</v>
@@ -2163,7 +2163,7 @@
         <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -2232,7 +2232,7 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
         <v>17</v>
@@ -2271,14 +2271,14 @@
         <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>3.55</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
         <v>2.66</v>
@@ -2327,13 +2327,13 @@
         <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O10" t="n">
         <v>1.02</v>
@@ -2342,19 +2342,19 @@
         <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="S10" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.17</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="I11" t="n">
         <v>1.6</v>
@@ -2548,7 +2548,7 @@
         <v>1.7</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V11" t="n">
         <v>2.62</v>
@@ -2557,7 +2557,7 @@
         <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
         <v>12.5</v>
@@ -2566,10 +2566,10 @@
         <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB11" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AC11" t="n">
         <v>12</v>
@@ -2584,10 +2584,10 @@
         <v>55</v>
       </c>
       <c r="AG11" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>30</v>
@@ -2611,7 +2611,7 @@
         <v>6.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.800000000000001</v>
@@ -2635,38 +2635,38 @@
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC11" t="n">
         <v>9</v>
       </c>
-      <c r="BC11" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
         <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>2.76</v>
       </c>
       <c r="K12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L12" t="n">
         <v>1.56</v>
@@ -2736,7 +2736,7 @@
         <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T12" t="n">
         <v>2.44</v>
@@ -2751,23 +2751,23 @@
         <v>1.86</v>
       </c>
       <c r="X12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC12" t="n">
         <v>7.4</v>
       </c>
-      <c r="Y12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AD12" t="n">
         <v>1000</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2811,56 +2811,56 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.22</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
         <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.18</v>
+        <v>11</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H13" t="n">
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -2933,10 +2933,10 @@
         <v>1.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
         <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3124,13 +3124,13 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.56</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.21</v>
@@ -3497,49 +3497,49 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S16" t="n">
         <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA16" t="n">
         <v>19.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
@@ -3551,10 +3551,10 @@
         <v>18.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AH16" t="n">
         <v>970</v>
@@ -3578,22 +3578,22 @@
         <v>65</v>
       </c>
       <c r="AO16" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AP16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS16" t="n">
         <v>5</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AT16" t="n">
         <v>5.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.9</v>
       </c>
       <c r="AU16" t="n">
         <v>10.5</v>
@@ -3602,41 +3602,41 @@
         <v>8.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AZ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA16" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA16" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BB16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC16" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC16" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>42</v>
+        <v>5.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3679,13 +3679,13 @@
         <v>2.58</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -3712,10 +3712,10 @@
         <v>1.87</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W17" t="n">
         <v>1.37</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>2.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="I18" t="n">
         <v>3.7</v>
@@ -3903,10 +3903,10 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
         <v>1.37</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
         <v>3.25</v>
@@ -4064,7 +4064,7 @@
         <v>2.38</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
@@ -4085,7 +4085,7 @@
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
         <v>1.83</v>
@@ -4196,7 +4196,7 @@
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4255,10 @@
         <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J20" t="n">
         <v>3.6</v>
@@ -4276,22 +4276,22 @@
         <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
         <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U20" t="n">
         <v>2.26</v>
@@ -4303,19 +4303,19 @@
         <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
         <v>50</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
         <v>8.199999999999999</v>
@@ -4330,7 +4330,7 @@
         <v>17.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
@@ -4366,7 +4366,7 @@
         <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -4390,7 +4390,7 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="BB20" t="n">
         <v>30</v>
@@ -4399,20 +4399,20 @@
         <v>23</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE20" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BF20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -4443,64 +4443,64 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
         <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="V21" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W21" t="n">
         <v>1.41</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
         <v>970</v>
@@ -4509,10 +4509,10 @@
         <v>30</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
         <v>12.5</v>
@@ -4551,7 +4551,7 @@
         <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
@@ -4560,13 +4560,13 @@
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT21" t="n">
         <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
         <v>10</v>
@@ -4575,19 +4575,19 @@
         <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4596,17 +4596,17 @@
         <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G22" t="n">
         <v>2.72</v>
       </c>
       <c r="H22" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I22" t="n">
         <v>3</v>
@@ -4652,7 +4652,7 @@
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -4679,7 +4679,7 @@
         <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U22" t="n">
         <v>2.3</v>
@@ -4706,7 +4706,7 @@
         <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
         <v>970</v>
@@ -4730,10 +4730,10 @@
         <v>44</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM22" t="n">
         <v>80</v>
@@ -4745,62 +4745,62 @@
         <v>23</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV22" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AW22" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.9</v>
+        <v>26</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H23" t="n">
         <v>5</v>
@@ -4843,10 +4843,10 @@
         <v>11.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="K23" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,34 +4855,34 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="S23" t="n">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4939,52 +4939,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I24" t="n">
         <v>3.6</v>
@@ -5082,7 +5082,7 @@
         <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z24" t="n">
         <v>22</v>
@@ -5097,7 +5097,7 @@
         <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE24" t="n">
         <v>75</v>
@@ -5136,13 +5136,13 @@
         <v>5.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
         <v>6.2</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX24" t="n">
         <v>14.5</v>
@@ -5166,29 +5166,29 @@
         <v>24</v>
       </c>
       <c r="BA24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF24" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G25" t="n">
         <v>2.6</v>
@@ -5234,16 +5234,16 @@
         <v>2.76</v>
       </c>
       <c r="K25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M25" t="n">
         <v>1.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>1.63</v>
@@ -5276,7 +5276,7 @@
         <v>7.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5327,28 +5327,28 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ25" t="n">
         <v>7</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -5357,32 +5357,32 @@
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD25" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -5437,28 +5437,28 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V26" t="n">
         <v>1.3</v>
@@ -5470,13 +5470,13 @@
         <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
         <v>30</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="n">
         <v>10</v>
@@ -5485,10 +5485,10 @@
         <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF26" t="n">
         <v>13</v>
@@ -5500,43 +5500,43 @@
         <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
         <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM26" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="AS26" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
         <v>15</v>
@@ -5545,38 +5545,38 @@
         <v>40</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY26" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>13.5</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>30</v>
       </c>
       <c r="BE26" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G27" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J27" t="n">
         <v>4.3</v>
       </c>
-      <c r="J27" t="n">
-        <v>4.2</v>
-      </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
@@ -5634,37 +5634,37 @@
         <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R27" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S27" t="n">
         <v>2.26</v>
       </c>
       <c r="T27" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U27" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X27" t="n">
         <v>36</v>
       </c>
       <c r="Y27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z27" t="n">
         <v>36</v>
@@ -5676,7 +5676,7 @@
         <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD27" t="n">
         <v>17.5</v>
@@ -5688,7 +5688,7 @@
         <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
         <v>16.5</v>
@@ -5697,19 +5697,19 @@
         <v>42</v>
       </c>
       <c r="AJ27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM27" t="n">
         <v>60</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AO27" t="n">
         <v>32</v>
@@ -5718,25 +5718,25 @@
         <v>20</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX27" t="n">
         <v>12.5</v>
@@ -5748,19 +5748,19 @@
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB27" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD27" t="n">
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF27" t="n">
         <v>6.8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -5810,10 +5810,10 @@
         <v>3.75</v>
       </c>
       <c r="I28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
@@ -5837,28 +5837,28 @@
         <v>1.64</v>
       </c>
       <c r="R28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S28" t="n">
         <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="U28" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="V28" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W28" t="n">
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y28" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
         <v>34</v>
@@ -5870,7 +5870,7 @@
         <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AQ28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX28" t="n">
         <v>6</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>5.8</v>
       </c>
       <c r="AY28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28" t="n">
         <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -6001,10 +6001,10 @@
         <v>3.15</v>
       </c>
       <c r="H29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6022,28 +6022,28 @@
         <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
         <v>1.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R29" t="n">
         <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T29" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U29" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W29" t="n">
         <v>1.46</v>
@@ -6055,10 +6055,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB29" t="n">
         <v>10.5</v>
@@ -6073,13 +6073,13 @@
         <v>29</v>
       </c>
       <c r="AF29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG29" t="n">
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI29" t="n">
         <v>46</v>
@@ -6094,22 +6094,22 @@
         <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN29" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO29" t="n">
         <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS29" t="n">
         <v>36</v>
@@ -6124,13 +6124,13 @@
         <v>11.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
         <v>18.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>18.5</v>
@@ -6142,23 +6142,23 @@
         <v>50</v>
       </c>
       <c r="BC29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD29" t="n">
         <v>50</v>
       </c>
       <c r="BE29" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>1.16</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
         <v>10.5</v>
@@ -6210,31 +6210,31 @@
         <v>1.21</v>
       </c>
       <c r="M30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O30" t="n">
         <v>1.12</v>
       </c>
       <c r="P30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R30" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T30" t="n">
         <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V30" t="n">
         <v>1.03</v>
@@ -6243,43 +6243,43 @@
         <v>7.4</v>
       </c>
       <c r="X30" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="Y30" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AD30" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AE30" t="n">
         <v>460</v>
       </c>
       <c r="AF30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG30" t="n">
         <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI30" t="n">
         <v>290</v>
       </c>
       <c r="AJ30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK30" t="n">
         <v>13.5</v>
@@ -6291,34 +6291,34 @@
         <v>270</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="AO30" t="n">
         <v>600</v>
       </c>
       <c r="AP30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT30" t="n">
         <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX30" t="n">
         <v>8</v>
@@ -6327,32 +6327,32 @@
         <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB30" t="n">
         <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD30" t="n">
         <v>36</v>
       </c>
       <c r="BE30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BG30" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -6616,13 +6616,13 @@
         <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
         <v>1.19</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="AR32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV32" t="n">
         <v>2</v>
       </c>
-      <c r="AS32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AW32" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="AX32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.91</v>
+        <v>2.44</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6777,16 @@
         <v>2.14</v>
       </c>
       <c r="H33" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I33" t="n">
         <v>7.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6804,13 +6804,13 @@
         <v>1.56</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="R33" t="n">
         <v>1.05</v>
       </c>
       <c r="S33" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G34" t="n">
         <v>2.22</v>
       </c>
       <c r="H34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I34" t="n">
         <v>5.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>3.5</v>
@@ -7109,7 +7109,7 @@
         <v>4.9</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC34" t="n">
         <v>20</v>
@@ -7121,14 +7121,14 @@
         <v>5</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG34" t="n">
         <v>4.9</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -760,7 +760,7 @@
         <v>3.25</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>2.24</v>
@@ -772,10 +772,10 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
@@ -793,16 +793,16 @@
         <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
         <v>1.62</v>
@@ -871,13 +871,13 @@
         <v>3.65</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.84</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="n">
         <v>3.55</v>
@@ -889,38 +889,38 @@
         <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.79</v>
+        <v>4.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.87</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -954,55 +954,55 @@
         <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
         <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
         <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1011,7 +1011,7 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1023,10 +1023,10 @@
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1035,7 +1035,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>1.82</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.3</v>
+        <v>1.85</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>1.81</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>1.74</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>1.74</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>1.79</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>1.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>1.81</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
         <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
         <v>1.5</v>
@@ -1175,7 +1175,7 @@
         <v>1.52</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q4" t="n">
         <v>2.38</v>
@@ -1190,13 +1190,13 @@
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>55</v>
@@ -1238,10 +1238,10 @@
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.4</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BD4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE4" t="n">
         <v>5.3</v>
       </c>
-      <c r="AX4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE4" t="n">
+      <c r="BF4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG4" t="n">
         <v>5.7</v>
       </c>
-      <c r="BF4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1363,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
@@ -1372,22 +1372,22 @@
         <v>1.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R5" t="n">
         <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
         <v>17.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -1686,17 +1686,17 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG6" t="n">
         <v>9.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>2.32</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.05</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1924,34 +1924,34 @@
         <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
         <v>2.24</v>
@@ -1960,7 +1960,7 @@
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1969,10 +1969,10 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -1987,7 +1987,7 @@
         <v>230</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -1999,7 +1999,7 @@
         <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
@@ -2023,68 +2023,68 @@
         <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>200</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.3</v>
+        <v>9.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.92</v>
+        <v>5.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.75</v>
+        <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.75</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.65</v>
+        <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.7</v>
+        <v>17</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2121,19 @@
         <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2145,16 +2145,16 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
         <v>1.73</v>
@@ -2163,7 +2163,7 @@
         <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -2172,40 +2172,40 @@
         <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
         <v>46</v>
       </c>
       <c r="AB9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>34</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
         <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK9" t="n">
         <v>40</v>
@@ -2220,7 +2220,7 @@
         <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
@@ -2232,7 +2232,7 @@
         <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
         <v>17</v>
@@ -2256,29 +2256,29 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="O10" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="Q10" t="n">
         <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -2521,10 +2521,10 @@
         <v>5.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
         <v>5.5</v>
@@ -2536,13 +2536,13 @@
         <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
         <v>1.7</v>
@@ -2551,7 +2551,7 @@
         <v>2.28</v>
       </c>
       <c r="V11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -2629,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>12.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         <v>1.16</v>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.69</v>
@@ -2733,7 +2733,7 @@
         <v>3.15</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S12" t="n">
         <v>6.8</v>
@@ -2751,22 +2751,22 @@
         <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2781,7 +2781,7 @@
         <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2790,7 +2790,7 @@
         <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2811,56 +2811,56 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AX12" t="n">
         <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="BB12" t="n">
         <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -2930,7 +2930,7 @@
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>990</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -3303,10 +3303,10 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
         <v>1.05</v>
@@ -3321,10 +3321,10 @@
         <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I16" t="n">
         <v>1.56</v>
@@ -3503,7 +3503,7 @@
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q16" t="n">
         <v>1.45</v>
@@ -3512,7 +3512,7 @@
         <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
@@ -3521,7 +3521,7 @@
         <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="W16" t="n">
         <v>1.16</v>
@@ -3545,7 +3545,7 @@
         <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE16" t="n">
         <v>18.5</v>
@@ -3560,7 +3560,7 @@
         <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ16" t="n">
         <v>170</v>
@@ -3575,13 +3575,13 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO16" t="n">
         <v>6</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>11</v>
@@ -3590,10 +3590,10 @@
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU16" t="n">
         <v>10.5</v>
@@ -3602,41 +3602,41 @@
         <v>8.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
         <v>5.8</v>
       </c>
-      <c r="BD16" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF16" t="n">
         <v>5.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.7</v>
       </c>
       <c r="BG16" t="n">
         <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>3.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I17" t="n">
         <v>2.58</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
         <v>3.35</v>
@@ -3697,7 +3697,7 @@
         <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
         <v>2.2</v>
@@ -3727,7 +3727,7 @@
         <v>9.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
         <v>38</v>
@@ -3739,19 +3739,19 @@
         <v>7.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG17" t="n">
         <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>50</v>
@@ -3775,7 +3775,7 @@
         <v>29</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ17" t="n">
         <v>8</v>
@@ -3784,7 +3784,7 @@
         <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
@@ -3796,41 +3796,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
         <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC17" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF17" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>36</v>
       </c>
       <c r="BG17" t="n">
         <v>22</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.3</v>
@@ -3936,7 +3936,7 @@
         <v>15.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
         <v>16</v>
@@ -3957,16 +3957,16 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -4020,11 +4020,11 @@
         <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
         <v>3.25</v>
@@ -4196,7 +4196,7 @@
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I20" t="n">
         <v>3.05</v>
@@ -4363,7 +4363,7 @@
         <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
@@ -4399,7 +4399,7 @@
         <v>23</v>
       </c>
       <c r="BD20" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
         <v>36</v>
@@ -4408,11 +4408,11 @@
         <v>18</v>
       </c>
       <c r="BG20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>2.22</v>
       </c>
       <c r="I21" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
@@ -4461,7 +4461,7 @@
         <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -4473,10 +4473,10 @@
         <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R21" t="n">
         <v>1.54</v>
@@ -4488,10 +4488,10 @@
         <v>1.6</v>
       </c>
       <c r="U21" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V21" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
         <v>1.41</v>
@@ -4518,7 +4518,7 @@
         <v>12.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
@@ -4530,7 +4530,7 @@
         <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ21" t="n">
         <v>60</v>
@@ -4542,7 +4542,7 @@
         <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN21" t="n">
         <v>28</v>
@@ -4551,7 +4551,7 @@
         <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
@@ -4560,7 +4560,7 @@
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT21" t="n">
         <v>13</v>
@@ -4575,38 +4575,38 @@
         <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
       </c>
       <c r="BD21" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
         <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -4643,10 +4643,10 @@
         <v>2.72</v>
       </c>
       <c r="H22" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
@@ -4670,7 +4670,7 @@
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
@@ -4700,13 +4700,13 @@
         <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB22" t="n">
         <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
         <v>970</v>
@@ -4727,10 +4727,10 @@
         <v>40</v>
       </c>
       <c r="AJ22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>42</v>
@@ -4739,7 +4739,7 @@
         <v>80</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AO22" t="n">
         <v>23</v>
@@ -4748,28 +4748,28 @@
         <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS22" t="n">
         <v>7.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -4790,7 +4790,7 @@
         <v>26</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="G23" t="n">
         <v>1.92</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I23" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,19 +4855,19 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="S23" t="n">
         <v>2.92</v>
@@ -4879,7 +4879,7 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W23" t="n">
         <v>2.08</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G24" t="n">
         <v>3.05</v>
@@ -5037,7 +5037,7 @@
         <v>3.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K24" t="n">
         <v>2.84</v>
@@ -5061,7 +5061,7 @@
         <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S24" t="n">
         <v>8.6</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -5219,25 +5219,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I25" t="n">
         <v>4.1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L25" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M25" t="n">
         <v>1.15</v>
@@ -5258,7 +5258,7 @@
         <v>1.15</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="T25" t="n">
         <v>2.26</v>
@@ -5270,7 +5270,7 @@
         <v>1.32</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X25" t="n">
         <v>7.6</v>
@@ -5345,7 +5345,7 @@
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW25" t="n">
         <v>5.2</v>
@@ -5366,7 +5366,7 @@
         <v>4.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BD25" t="n">
         <v>5.2</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G26" t="n">
         <v>2.04</v>
@@ -5422,7 +5422,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
         <v>3.8</v>
@@ -5437,16 +5437,16 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R26" t="n">
         <v>1.42</v>
@@ -5455,28 +5455,28 @@
         <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U26" t="n">
         <v>2.24</v>
       </c>
       <c r="V26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y26" t="n">
         <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
         <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
         <v>13</v>
@@ -5518,10 +5518,10 @@
         <v>13</v>
       </c>
       <c r="AO26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>14.5</v>
@@ -5530,7 +5530,7 @@
         <v>27</v>
       </c>
       <c r="AS26" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT26" t="n">
         <v>9.199999999999999</v>
@@ -5548,13 +5548,13 @@
         <v>12</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
@@ -5563,10 +5563,10 @@
         <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE26" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H27" t="n">
         <v>4.1</v>
@@ -5625,7 +5625,7 @@
         <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
@@ -5652,13 +5652,13 @@
         <v>1.54</v>
       </c>
       <c r="U27" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X27" t="n">
         <v>36</v>
@@ -5667,10 +5667,10 @@
         <v>26</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB27" t="n">
         <v>15</v>
@@ -5679,10 +5679,10 @@
         <v>11.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF27" t="n">
         <v>15</v>
@@ -5721,10 +5721,10 @@
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
@@ -5736,7 +5736,7 @@
         <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX27" t="n">
         <v>12.5</v>
@@ -5745,10 +5745,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BB27" t="n">
         <v>17.5</v>
@@ -5760,17 +5760,17 @@
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G28" t="n">
         <v>1.99</v>
@@ -5810,7 +5810,7 @@
         <v>3.75</v>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>3.95</v>
@@ -5855,13 +5855,13 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Y28" t="n">
         <v>950</v>
       </c>
       <c r="Z28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -5915,37 +5915,37 @@
         <v>17</v>
       </c>
       <c r="AR28" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC28" t="n">
         <v>15</v>
@@ -5954,17 +5954,17 @@
         <v>19</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
         <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I29" t="n">
         <v>2.62</v>
@@ -6022,13 +6022,13 @@
         <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P29" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>1.29</v>
@@ -6037,16 +6037,16 @@
         <v>4.2</v>
       </c>
       <c r="T29" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U29" t="n">
         <v>2.02</v>
       </c>
       <c r="V29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X29" t="n">
         <v>11</v>
@@ -6055,10 +6055,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB29" t="n">
         <v>10.5</v>
@@ -6124,13 +6124,13 @@
         <v>11.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
         <v>18.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ29" t="n">
         <v>18.5</v>
@@ -6154,11 +6154,11 @@
         <v>38</v>
       </c>
       <c r="BG29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G30" t="n">
         <v>1.16</v>
@@ -6198,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
         <v>10.5</v>
       </c>
       <c r="K30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="L30" t="n">
         <v>1.21</v>
@@ -6213,7 +6213,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.12</v>
@@ -6228,10 +6228,10 @@
         <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
         <v>1.76</v>
@@ -6249,7 +6249,7 @@
         <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
@@ -6264,22 +6264,22 @@
         <v>950</v>
       </c>
       <c r="AE30" t="n">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="AF30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AG30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>950</v>
       </c>
       <c r="AI30" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AJ30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AK30" t="n">
         <v>13.5</v>
@@ -6288,13 +6288,13 @@
         <v>42</v>
       </c>
       <c r="AM30" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN30" t="n">
         <v>2.82</v>
       </c>
       <c r="AO30" t="n">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="AP30" t="n">
         <v>10.5</v>
@@ -6309,7 +6309,7 @@
         <v>12.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>20</v>
@@ -6318,13 +6318,13 @@
         <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX30" t="n">
         <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>40</v>
@@ -6348,11 +6348,11 @@
         <v>2.62</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
         <v>1.84</v>
@@ -6586,25 +6586,25 @@
         <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
         <v>4.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
         <v>1.69</v>
@@ -6616,7 +6616,7 @@
         <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T32" t="n">
         <v>2.04</v>
@@ -6625,7 +6625,7 @@
         <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W32" t="n">
         <v>2.16</v>
@@ -6685,28 +6685,28 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AT32" t="n">
         <v>3.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="AV32" t="n">
         <v>2</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="AX32" t="n">
         <v>4.4</v>
@@ -6715,32 +6715,32 @@
         <v>3.15</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="BB32" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.16</v>
+        <v>1.74</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -6807,16 +6807,16 @@
         <v>1.94</v>
       </c>
       <c r="R33" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="S33" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
         <v>1.16</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -6974,10 +6974,10 @@
         <v>4.3</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
         <v>3.5</v>
@@ -6998,16 +6998,16 @@
         <v>1.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
         <v>1.74</v>
@@ -7016,7 +7016,7 @@
         <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X34" t="n">
         <v>11</v>
@@ -7031,10 +7031,10 @@
         <v>150</v>
       </c>
       <c r="AB34" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD34" t="n">
         <v>21</v>
@@ -7061,7 +7061,7 @@
         <v>30</v>
       </c>
       <c r="AL34" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM34" t="n">
         <v>230</v>
@@ -7073,16 +7073,16 @@
         <v>150</v>
       </c>
       <c r="AP34" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ34" t="n">
         <v>10</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT34" t="n">
         <v>5.9</v>
@@ -7091,44 +7091,44 @@
         <v>6.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ34" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -757,31 +757,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
@@ -793,7 +793,7 @@
         <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
         <v>4.1</v>
@@ -805,7 +805,7 @@
         <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
         <v>1.34</v>
@@ -850,77 +850,77 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR2" t="n">
         <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB2" t="n">
         <v>3.55</v>
       </c>
-      <c r="AV2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BC2" t="n">
-        <v>2.02</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.02</v>
+        <v>3.55</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.02</v>
+        <v>5.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -984,7 +984,7 @@
         <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -993,16 +993,16 @@
         <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.86</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.81</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1026,7 +1026,7 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1035,7 +1035,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1044,10 +1044,10 @@
         <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.85</v>
+        <v>5.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.74</v>
+        <v>3.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.79</v>
+        <v>2.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
         <v>2.9</v>
@@ -1169,22 +1169,22 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
         <v>1.52</v>
       </c>
       <c r="P4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I6" t="n">
         <v>1.96</v>
@@ -1551,7 +1551,7 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1626,7 +1626,7 @@
         <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
@@ -1641,7 +1641,7 @@
         <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.800000000000001</v>
@@ -1665,7 +1665,7 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>15.5</v>
@@ -1677,26 +1677,26 @@
         <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>8</v>
       </c>
-      <c r="BD6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF6" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
         <v>9.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         <v>3.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
         <v>6.4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
@@ -1960,7 +1960,7 @@
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1972,7 +1972,7 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -1987,7 +1987,7 @@
         <v>230</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -1999,13 +1999,13 @@
         <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>130</v>
@@ -2023,22 +2023,22 @@
         <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP8" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
         <v>5.9</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -2062,29 +2062,29 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J9" t="n">
         <v>3.35</v>
@@ -2133,7 +2133,7 @@
         <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2145,10 +2145,10 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.93</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
@@ -2163,7 +2163,7 @@
         <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -2208,7 +2208,7 @@
         <v>50</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
@@ -2217,7 +2217,7 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
         <v>25</v>
@@ -2256,7 +2256,7 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
         <v>6.4</v>
@@ -2265,20 +2265,20 @@
         <v>6.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF9" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -2333,10 +2333,10 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
         <v>1.59</v>
@@ -2354,7 +2354,7 @@
         <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
@@ -2384,7 +2384,7 @@
         <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2432,7 +2432,7 @@
         <v>2.92</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="AV10" t="n">
         <v>3.65</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.28</v>
@@ -2533,7 +2533,7 @@
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q11" t="n">
         <v>1.54</v>
@@ -2542,19 +2542,19 @@
         <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U11" t="n">
         <v>2.28</v>
       </c>
       <c r="V11" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -2581,7 +2581,7 @@
         <v>970</v>
       </c>
       <c r="AF11" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AG11" t="n">
         <v>950</v>
@@ -2638,35 +2638,35 @@
         <v>8.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE11" t="n">
-        <v>9</v>
-      </c>
       <c r="BF11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
         <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -2715,19 +2715,19 @@
         <v>2.94</v>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N12" t="n">
         <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
         <v>3.15</v>
@@ -2757,7 +2757,7 @@
         <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2790,7 +2790,7 @@
         <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2811,10 +2811,10 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AT12" t="n">
         <v>5.2</v>
@@ -2826,41 +2826,41 @@
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY12" t="n">
         <v>5.5</v>
       </c>
       <c r="AZ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB12" t="n">
         <v>7.4</v>
       </c>
-      <c r="BA12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>10</v>
-      </c>
       <c r="BC12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -2891,103 +2891,103 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="G13" t="n">
-        <v>990</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="I13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI13" t="n">
         <v>110</v>
       </c>
-      <c r="J13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>950</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ13" t="n">
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3085,76 +3085,76 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="G14" t="n">
-        <v>990</v>
+        <v>1.37</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>990</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.09</v>
       </c>
-      <c r="K14" t="n">
-        <v>950</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>1.45</v>
+        <v>4.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3163,10 +3163,10 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3175,10 +3175,10 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3187,68 +3187,68 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>990</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="I15" t="n">
-        <v>990</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1.54</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G16" t="n">
         <v>7.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.56</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K16" t="n">
         <v>5.6</v>
@@ -3497,19 +3497,19 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
         <v>1.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
         <v>2.12</v>
@@ -3521,7 +3521,7 @@
         <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="W16" t="n">
         <v>1.16</v>
@@ -3542,7 +3542,7 @@
         <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
         <v>10.5</v>
@@ -3560,7 +3560,7 @@
         <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ16" t="n">
         <v>170</v>
@@ -3581,7 +3581,7 @@
         <v>6</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ16" t="n">
         <v>11</v>
@@ -3590,53 +3590,53 @@
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU16" t="n">
         <v>10.5</v>
       </c>
       <c r="AV16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW16" t="n">
         <v>8.6</v>
       </c>
-      <c r="AW16" t="n">
-        <v>5</v>
-      </c>
       <c r="AX16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
         <v>6</v>
       </c>
-      <c r="BD16" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG16" t="n">
         <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -3793,7 +3793,7 @@
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AW17" t="n">
         <v>7.8</v>
@@ -3802,7 +3802,7 @@
         <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="AZ17" t="n">
         <v>16</v>
@@ -3826,11 +3826,11 @@
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="n">
         <v>2.38</v>
       </c>
       <c r="I19" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
@@ -4079,22 +4079,22 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
         <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
         <v>1.66</v>
@@ -4103,10 +4103,10 @@
         <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
@@ -4115,10 +4115,10 @@
         <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="n">
         <v>15.5</v>
@@ -4127,7 +4127,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -4142,7 +4142,7 @@
         <v>19.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ19" t="n">
         <v>55</v>
@@ -4160,7 +4160,7 @@
         <v>32</v>
       </c>
       <c r="AO19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP19" t="n">
         <v>11.5</v>
@@ -4169,10 +4169,10 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>27</v>
+        <v>4.5</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>18.5</v>
@@ -4196,7 +4196,7 @@
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
@@ -4205,10 +4205,10 @@
         <v>22</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF19" t="n">
         <v>18.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4252,10 @@
         <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I20" t="n">
         <v>3.05</v>
@@ -4273,7 +4273,7 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O20" t="n">
         <v>1.3</v>
@@ -4288,7 +4288,7 @@
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
         <v>1.74</v>
@@ -4363,10 +4363,10 @@
         <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -4390,7 +4390,7 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
         <v>30</v>
@@ -4402,7 +4402,7 @@
         <v>32</v>
       </c>
       <c r="BE20" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF20" t="n">
         <v>18</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
         <v>19</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
         <v>12.5</v>
@@ -4545,13 +4545,13 @@
         <v>65</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
@@ -4560,10 +4560,10 @@
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
         <v>8</v>
@@ -4575,38 +4575,38 @@
         <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BD21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF21" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
         <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
         <v>40</v>
       </c>
       <c r="AJ22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK22" t="n">
         <v>28</v>
@@ -4748,25 +4748,25 @@
         <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
         <v>7.2</v>
       </c>
       <c r="AT22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV22" t="n">
         <v>5.3</v>
       </c>
-      <c r="AU22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
         <v>6.2</v>
@@ -4775,22 +4775,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC22" t="n">
         <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="BE22" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="G23" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="H23" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="P23" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R23" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>2.92</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -5043,22 +5043,22 @@
         <v>2.84</v>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="N24" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="P24" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
         <v>1.11</v>
@@ -5067,10 +5067,10 @@
         <v>8.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="U24" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
         <v>1.39</v>
@@ -5085,13 +5085,13 @@
         <v>8.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
         <v>80</v>
       </c>
       <c r="AB24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
@@ -5100,7 +5100,7 @@
         <v>19.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AF24" t="n">
         <v>19.5</v>
@@ -5109,7 +5109,7 @@
         <v>18.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AI24" t="n">
         <v>140</v>
@@ -5130,10 +5130,10 @@
         <v>95</v>
       </c>
       <c r="AO24" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>6.8</v>
@@ -5142,10 +5142,10 @@
         <v>18.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
         <v>14.5</v>
@@ -5166,29 +5166,29 @@
         <v>24</v>
       </c>
       <c r="BA24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE24" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>8</v>
-      </c>
       <c r="BF24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
         <v>7.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>2.66</v>
       </c>
       <c r="H25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I25" t="n">
         <v>4.1</v>
@@ -5234,28 +5234,28 @@
         <v>2.78</v>
       </c>
       <c r="K25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M25" t="n">
         <v>1.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O25" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="P25" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S25" t="n">
         <v>6.6</v>
@@ -5276,7 +5276,7 @@
         <v>7.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5312,7 +5312,7 @@
         <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
@@ -5327,28 +5327,28 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ25" t="n">
         <v>7</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -5357,32 +5357,32 @@
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD25" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF25" t="n">
         <v>32</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>2.04</v>
@@ -5422,7 +5422,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>3.8</v>
@@ -5437,7 +5437,7 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
@@ -5446,22 +5446,22 @@
         <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R26" t="n">
         <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
         <v>2.24</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
         <v>1.95</v>
@@ -5470,7 +5470,7 @@
         <v>17</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z26" t="n">
         <v>36</v>
@@ -5509,7 +5509,7 @@
         <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>85</v>
@@ -5518,7 +5518,7 @@
         <v>13</v>
       </c>
       <c r="AO26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP26" t="n">
         <v>15.5</v>
@@ -5527,7 +5527,7 @@
         <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="AS26" t="n">
         <v>14.5</v>
@@ -5542,7 +5542,7 @@
         <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="AX26" t="n">
         <v>12</v>
@@ -5551,10 +5551,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
@@ -5563,7 +5563,7 @@
         <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BE26" t="n">
         <v>14.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G27" t="n">
         <v>1.85</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
         <v>4.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
         <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
@@ -5646,7 +5646,7 @@
         <v>1.66</v>
       </c>
       <c r="S27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T27" t="n">
         <v>1.54</v>
@@ -5697,10 +5697,10 @@
         <v>42</v>
       </c>
       <c r="AJ27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL27" t="n">
         <v>26</v>
@@ -5709,7 +5709,7 @@
         <v>60</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO27" t="n">
         <v>32</v>
@@ -5721,10 +5721,10 @@
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
@@ -5736,7 +5736,7 @@
         <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>12.5</v>
@@ -5748,7 +5748,7 @@
         <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
         <v>17.5</v>
@@ -5760,17 +5760,17 @@
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF27" t="n">
         <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G28" t="n">
         <v>1.99</v>
       </c>
       <c r="H28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I28" t="n">
         <v>4.4</v>
@@ -5819,7 +5819,7 @@
         <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M28" t="n">
         <v>1.03</v>
@@ -5915,37 +5915,37 @@
         <v>17</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV28" t="n">
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA28" t="n">
         <v>8</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>15</v>
@@ -5954,17 +5954,17 @@
         <v>19</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF28" t="n">
         <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H29" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="I29" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6013,22 +6013,22 @@
         <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R29" t="n">
         <v>1.29</v>
@@ -6037,16 +6037,16 @@
         <v>4.2</v>
       </c>
       <c r="T29" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V29" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W29" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X29" t="n">
         <v>11</v>
@@ -6055,13 +6055,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC29" t="n">
         <v>7.2</v>
@@ -6070,13 +6070,13 @@
         <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH29" t="n">
         <v>19.5</v>
@@ -6097,22 +6097,22 @@
         <v>100</v>
       </c>
       <c r="AN29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT29" t="n">
         <v>10</v>
@@ -6124,19 +6124,19 @@
         <v>11.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>18.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB29" t="n">
         <v>50</v>
@@ -6154,11 +6154,11 @@
         <v>38</v>
       </c>
       <c r="BG29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="G30" t="n">
         <v>1.16</v>
@@ -6198,7 +6198,7 @@
         <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
         <v>10.5</v>
@@ -6213,7 +6213,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O30" t="n">
         <v>1.12</v>
@@ -6231,7 +6231,7 @@
         <v>1.94</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
         <v>1.76</v>
@@ -6279,7 +6279,7 @@
         <v>270</v>
       </c>
       <c r="AJ30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK30" t="n">
         <v>13.5</v>
@@ -6291,22 +6291,22 @@
         <v>260</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AO30" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6315,10 +6315,10 @@
         <v>20</v>
       </c>
       <c r="AV30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX30" t="n">
         <v>8</v>
@@ -6330,7 +6330,7 @@
         <v>40</v>
       </c>
       <c r="BA30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB30" t="n">
         <v>8</v>
@@ -6342,17 +6342,17 @@
         <v>36</v>
       </c>
       <c r="BE30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BG30" t="n">
         <v>20</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="G31" t="n">
         <v>1000</v>
@@ -6392,13 +6392,13 @@
         <v>1.09</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J31" t="n">
         <v>1.09</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G32" t="n">
         <v>1.84</v>
@@ -6592,10 +6592,10 @@
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -6619,7 +6619,7 @@
         <v>3.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
         <v>1.79</v>
@@ -6649,7 +6649,7 @@
         <v>970</v>
       </c>
       <c r="AD32" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
@@ -6661,7 +6661,7 @@
         <v>970</v>
       </c>
       <c r="AH32" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6688,7 +6688,7 @@
         <v>3.35</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.55</v>
+        <v>2.38</v>
       </c>
       <c r="AR32" t="n">
         <v>1.7</v>
@@ -6724,7 +6724,7 @@
         <v>2.46</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="BD32" t="n">
         <v>1.71</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -6771,170 +6771,170 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="H33" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="I33" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P33" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="R33" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
         <v>10</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS34" t="n">
         <v>5.8</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -760,55 +760,55 @@
         <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
         <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -820,7 +820,7 @@
         <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -850,77 +850,77 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
         <v>70</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>85</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.55</v>
+        <v>1.89</v>
       </c>
       <c r="BC2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG2" t="n">
         <v>5.6</v>
       </c>
-      <c r="BD2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
         <v>4.9</v>
@@ -969,19 +969,19 @@
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
         <v>2.16</v>
@@ -993,10 +993,10 @@
         <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
         <v>1.25</v>
@@ -1044,10 +1044,10 @@
         <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="AS3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4</v>
-      </c>
       <c r="AW3" t="n">
-        <v>2.36</v>
+        <v>1.72</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AY3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.24</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BD3" t="n">
-        <v>2.68</v>
+        <v>1.76</v>
       </c>
       <c r="BE3" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.76</v>
       </c>
-      <c r="BF3" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BG3" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1160,16 +1160,16 @@
         <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
         <v>1.52</v>
@@ -1178,31 +1178,31 @@
         <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
         <v>10</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>21</v>
@@ -1211,10 +1211,10 @@
         <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1253,62 +1253,62 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1339,40 +1339,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="G5" t="n">
-        <v>990</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>990</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R5" t="n">
         <v>1.28</v>
@@ -1387,13 +1387,13 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1450,59 +1450,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1533,118 +1533,118 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I6" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
         <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF6" t="n">
         <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
         <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
         <v>11</v>
@@ -1653,7 +1653,7 @@
         <v>17.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -1662,41 +1662,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AY6" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q7" t="n">
         <v>2.5</v>
@@ -1766,7 +1766,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
         <v>2.26</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
         <v>1.86</v>
@@ -1942,10 +1942,10 @@
         <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -1954,16 +1954,16 @@
         <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
         <v>1.76</v>
@@ -1972,13 +1972,13 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="n">
         <v>60</v>
@@ -1987,7 +1987,7 @@
         <v>230</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -1999,10 +1999,10 @@
         <v>130</v>
       </c>
       <c r="AF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG8" t="n">
         <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>29</v>
@@ -2035,10 +2035,10 @@
         <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
         <v>5.9</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -2062,7 +2062,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2071,20 +2071,20 @@
         <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2115,73 +2115,73 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U9" t="n">
         <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
         <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.4</v>
@@ -2190,10 +2190,10 @@
         <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
@@ -2202,13 +2202,13 @@
         <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
@@ -2217,10 +2217,10 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AO9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
@@ -2229,7 +2229,7 @@
         <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>6.4</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
         <v>17</v>
@@ -2256,13 +2256,13 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
         <v>6.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2318,22 +2318,22 @@
         <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="O10" t="n">
         <v>1.44</v>
@@ -2348,16 +2348,16 @@
         <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
         <v>1.8</v>
@@ -2420,10 +2420,10 @@
         <v>3.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS10" t="n">
         <v>4.2</v>
@@ -2441,7 +2441,7 @@
         <v>4.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AY10" t="n">
         <v>3.3</v>
@@ -2450,16 +2450,16 @@
         <v>3.75</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE10" t="n">
         <v>4.2</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G11" t="n">
         <v>7.2</v>
@@ -2512,37 +2512,37 @@
         <v>1.51</v>
       </c>
       <c r="I11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
         <v>1.71</v>
@@ -2551,13 +2551,13 @@
         <v>2.28</v>
       </c>
       <c r="V11" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W11" t="n">
         <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Y11" t="n">
         <v>12.5</v>
@@ -2566,7 +2566,7 @@
         <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB11" t="n">
         <v>950</v>
@@ -2578,28 +2578,28 @@
         <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AF11" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AG11" t="n">
         <v>950</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AJ11" t="n">
         <v>180</v>
       </c>
       <c r="AK11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
         <v>85</v>
@@ -2608,10 +2608,10 @@
         <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.800000000000001</v>
@@ -2620,10 +2620,10 @@
         <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
@@ -2635,38 +2635,38 @@
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD11" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
         <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2700,61 +2700,61 @@
         <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
         <v>1.17</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="P12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S12" t="n">
         <v>6.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
         <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2781,13 +2781,13 @@
         <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2811,10 +2811,10 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="AT12" t="n">
         <v>5.2</v>
@@ -2826,41 +2826,41 @@
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>7.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>1.44</v>
       </c>
       <c r="I13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -2909,7 +2909,7 @@
         <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
@@ -2918,13 +2918,13 @@
         <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
@@ -2936,7 +2936,7 @@
         <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
         <v>2.78</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3085,124 +3085,124 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="G14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
         <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z14" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AK14" t="n">
         <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT14" t="n">
         <v>4.3</v>
@@ -3211,44 +3211,44 @@
         <v>10</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
         <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3279,76 +3279,76 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="G15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z15" t="n">
         <v>11</v>
       </c>
-      <c r="Z15" t="n">
-        <v>12</v>
-      </c>
       <c r="AA15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
         <v>12</v>
@@ -3363,86 +3363,86 @@
         <v>30</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AK15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL15" t="n">
         <v>110</v>
       </c>
-      <c r="AL15" t="n">
-        <v>100</v>
-      </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AO15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.75</v>
+        <v>21</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.7</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I16" t="n">
         <v>1.56</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
@@ -3524,10 +3524,10 @@
         <v>2.78</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -3536,19 +3536,19 @@
         <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB16" t="n">
         <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
         <v>10.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF16" t="n">
         <v>60</v>
@@ -3575,25 +3575,25 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="AR16" t="n">
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU16" t="n">
         <v>10.5</v>
@@ -3608,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3617,26 +3617,26 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
         <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3670,28 +3670,28 @@
         <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H17" t="n">
         <v>2.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
@@ -3700,13 +3700,13 @@
         <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
         <v>1.87</v>
@@ -3766,7 +3766,7 @@
         <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN17" t="n">
         <v>55</v>
@@ -3775,7 +3775,7 @@
         <v>29</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>8</v>
@@ -3814,7 +3814,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD17" t="n">
         <v>8</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="n">
         <v>2.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J18" t="n">
         <v>3.45</v>
@@ -3879,25 +3879,25 @@
         <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
         <v>3.2</v>
@@ -3969,7 +3969,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
         <v>12</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX18" t="n">
         <v>13</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
         <v>2.38</v>
@@ -4070,58 +4070,58 @@
         <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
         <v>1.64</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
         <v>40</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
         <v>9.800000000000001</v>
@@ -4136,13 +4136,13 @@
         <v>25</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ19" t="n">
         <v>55</v>
@@ -4151,7 +4151,7 @@
         <v>38</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4163,22 +4163,22 @@
         <v>22</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
       </c>
       <c r="AR19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT19" t="n">
         <v>12</v>
       </c>
-      <c r="AS19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
@@ -4187,38 +4187,38 @@
         <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
       </c>
       <c r="BC19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>22</v>
       </c>
-      <c r="BD19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BG19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="H20" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="I20" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="J20" t="n">
         <v>3.6</v>
@@ -4267,13 +4267,13 @@
         <v>3.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.3</v>
@@ -4288,19 +4288,19 @@
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X20" t="n">
         <v>15</v>
@@ -4309,22 +4309,22 @@
         <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
         <v>17.5</v>
@@ -4336,7 +4336,7 @@
         <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ20" t="n">
         <v>38</v>
@@ -4348,13 +4348,13 @@
         <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="n">
         <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
         <v>14</v>
@@ -4363,16 +4363,16 @@
         <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
@@ -4381,7 +4381,7 @@
         <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
         <v>10.5</v>
@@ -4390,13 +4390,13 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>32</v>
@@ -4405,14 +4405,14 @@
         <v>48</v>
       </c>
       <c r="BF20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG20" t="n">
         <v>23</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
         <v>2.22</v>
       </c>
       <c r="I21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
@@ -4461,43 +4461,43 @@
         <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P21" t="n">
         <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R21" t="n">
         <v>1.54</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U21" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V21" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
         <v>950</v>
@@ -4509,10 +4509,10 @@
         <v>30</v>
       </c>
       <c r="AB21" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
         <v>12.5</v>
@@ -4560,7 +4560,7 @@
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -4575,7 +4575,7 @@
         <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
@@ -4584,29 +4584,29 @@
         <v>7.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG21" t="n">
         <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4643,40 +4643,40 @@
         <v>2.72</v>
       </c>
       <c r="H22" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I22" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
         <v>1.7</v>
@@ -4685,13 +4685,13 @@
         <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
         <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y22" t="n">
         <v>970</v>
@@ -4712,7 +4712,7 @@
         <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
         <v>970</v>
@@ -4742,55 +4742,55 @@
         <v>970</v>
       </c>
       <c r="AO22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX22" t="n">
         <v>6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>6.2</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA22" t="n">
         <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="G23" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O23" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P23" t="n">
         <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V23" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X23" t="n">
         <v>10.5</v>
@@ -4894,19 +4894,19 @@
         <v>60</v>
       </c>
       <c r="AA23" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB23" t="n">
         <v>6.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
         <v>34</v>
       </c>
       <c r="AE23" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF23" t="n">
         <v>10.5</v>
@@ -4918,7 +4918,7 @@
         <v>34</v>
       </c>
       <c r="AI23" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
@@ -4930,71 +4930,71 @@
         <v>75</v>
       </c>
       <c r="AM23" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN23" t="n">
         <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="AQ23" t="n">
         <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS23" t="n">
         <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV23" t="n">
         <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB23" t="n">
         <v>13.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
         <v>4.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG23" t="n">
         <v>4.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J24" t="n">
         <v>2.64</v>
       </c>
       <c r="K24" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="L24" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
         <v>1.21</v>
       </c>
       <c r="N24" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="P24" t="n">
         <v>1.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
         <v>1.11</v>
       </c>
       <c r="S24" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>2.66</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.5</v>
+        <v>1.12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.8</v>
+        <v>1.13</v>
       </c>
       <c r="AR24" t="n">
-        <v>18.5</v>
+        <v>1.13</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.2</v>
+        <v>1.13</v>
       </c>
       <c r="AT24" t="n">
-        <v>6</v>
+        <v>1.13</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>1.13</v>
       </c>
       <c r="AV24" t="n">
-        <v>15</v>
+        <v>1.06</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.2</v>
+        <v>1.13</v>
       </c>
       <c r="AX24" t="n">
-        <v>14.5</v>
+        <v>1.13</v>
       </c>
       <c r="AY24" t="n">
-        <v>13.5</v>
+        <v>1.06</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>1.12</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.6</v>
+        <v>1.13</v>
       </c>
       <c r="BB24" t="n">
-        <v>7</v>
+        <v>1.13</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>1.13</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.4</v>
+        <v>1.13</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>1.13</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.4</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.6</v>
+        <v>1.12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -5222,58 +5222,58 @@
         <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="O25" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="P25" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="n">
         <v>9.6</v>
@@ -5300,7 +5300,7 @@
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -5312,7 +5312,7 @@
         <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
@@ -5327,28 +5327,28 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ25" t="n">
         <v>7</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
         <v>11.5</v>
@@ -5357,32 +5357,32 @@
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC25" t="n">
         <v>4.8</v>
       </c>
-      <c r="BA25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB25" t="n">
+      <c r="BD25" t="n">
         <v>5</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BE25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG25" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -5416,79 +5416,79 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K26" t="n">
         <v>4</v>
       </c>
-      <c r="I26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U26" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
         <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF26" t="n">
         <v>13</v>
@@ -5497,7 +5497,7 @@
         <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
         <v>55</v>
@@ -5506,46 +5506,46 @@
         <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM26" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="AS26" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
         <v>9.6</v>
@@ -5554,7 +5554,7 @@
         <v>15.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
@@ -5563,20 +5563,20 @@
         <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BE26" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BF26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G27" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
         <v>4.4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
@@ -5634,22 +5634,22 @@
         <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
         <v>2.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S27" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U27" t="n">
         <v>2.58</v>
@@ -5658,7 +5658,7 @@
         <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X27" t="n">
         <v>36</v>
@@ -5670,7 +5670,7 @@
         <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB27" t="n">
         <v>15</v>
@@ -5679,7 +5679,7 @@
         <v>11.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE27" t="n">
         <v>46</v>
@@ -5694,7 +5694,7 @@
         <v>16.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ27" t="n">
         <v>21</v>
@@ -5703,7 +5703,7 @@
         <v>17</v>
       </c>
       <c r="AL27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM27" t="n">
         <v>60</v>
@@ -5712,31 +5712,31 @@
         <v>7.6</v>
       </c>
       <c r="AO27" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP27" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="AQ27" t="n">
         <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AS27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX27" t="n">
         <v>12.5</v>
@@ -5748,7 +5748,7 @@
         <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB27" t="n">
         <v>17.5</v>
@@ -5760,17 +5760,17 @@
         <v>20</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -5801,55 +5801,55 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="G28" t="n">
         <v>1.99</v>
       </c>
       <c r="H28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
         <v>1.19</v>
       </c>
       <c r="P28" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.64</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.6</v>
-      </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="T28" t="n">
         <v>1.56</v>
       </c>
       <c r="U28" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
         <v>2</v>
@@ -5867,13 +5867,13 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC28" t="n">
         <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
@@ -5882,7 +5882,7 @@
         <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
         <v>970</v>
@@ -5891,7 +5891,7 @@
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK28" t="n">
         <v>970</v>
@@ -5903,37 +5903,37 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY28" t="n">
         <v>9.199999999999999</v>
@@ -5942,29 +5942,29 @@
         <v>6.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BB28" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BC28" t="n">
         <v>15</v>
       </c>
       <c r="BD28" t="n">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF28" t="n">
         <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H29" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="I29" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6013,22 +6013,22 @@
         <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P29" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>1.29</v>
@@ -6043,19 +6043,19 @@
         <v>2.04</v>
       </c>
       <c r="V29" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W29" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X29" t="n">
         <v>11</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
         <v>36</v>
@@ -6073,64 +6073,64 @@
         <v>28</v>
       </c>
       <c r="AF29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ29" t="n">
         <v>55</v>
       </c>
       <c r="AK29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="n">
         <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW29" t="n">
         <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ29" t="n">
         <v>18.5</v>
@@ -6142,23 +6142,23 @@
         <v>50</v>
       </c>
       <c r="BC29" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD29" t="n">
         <v>50</v>
       </c>
       <c r="BE29" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF29" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
         <v>10.5</v>
@@ -6219,13 +6219,13 @@
         <v>1.12</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q30" t="n">
         <v>1.37</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S30" t="n">
         <v>1.94</v>
@@ -6249,7 +6249,7 @@
         <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
@@ -6264,7 +6264,7 @@
         <v>950</v>
       </c>
       <c r="AE30" t="n">
-        <v>420</v>
+        <v>530</v>
       </c>
       <c r="AF30" t="n">
         <v>9.199999999999999</v>
@@ -6276,7 +6276,7 @@
         <v>950</v>
       </c>
       <c r="AI30" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AJ30" t="n">
         <v>9.199999999999999</v>
@@ -6288,7 +6288,7 @@
         <v>42</v>
       </c>
       <c r="AM30" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN30" t="n">
         <v>2.8</v>
@@ -6297,16 +6297,16 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>11</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AR30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS30" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>13</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6327,10 +6327,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BA30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB30" t="n">
         <v>8</v>
@@ -6342,17 +6342,17 @@
         <v>36</v>
       </c>
       <c r="BE30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BG30" t="n">
         <v>20</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -6583,40 +6583,40 @@
         <v>1.84</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K32" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
         <v>1.41</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
@@ -6625,10 +6625,10 @@
         <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X32" t="n">
         <v>970</v>
@@ -6688,7 +6688,7 @@
         <v>3.35</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="AR32" t="n">
         <v>1.7</v>
@@ -6724,7 +6724,7 @@
         <v>2.46</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="BD32" t="n">
         <v>1.71</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -6771,170 +6771,170 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="G33" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="H33" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R33" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T33" t="n">
         <v>1.98</v>
       </c>
       <c r="U33" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="W33" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="X33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z33" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA33" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AB33" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC33" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE33" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG33" t="n">
         <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL33" t="n">
         <v>55</v>
       </c>
       <c r="AM33" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>4</v>
       </c>
-      <c r="AS33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA33" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>14</v>
+        <v>3.95</v>
       </c>
       <c r="BC33" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="BD33" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G34" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H34" t="n">
         <v>4.3</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>3.05</v>
@@ -6983,28 +6983,28 @@
         <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N34" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P34" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T34" t="n">
         <v>2.08</v>
@@ -7013,7 +7013,7 @@
         <v>1.74</v>
       </c>
       <c r="V34" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W34" t="n">
         <v>1.83</v>
@@ -7022,7 +7022,7 @@
         <v>11</v>
       </c>
       <c r="Y34" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
         <v>40</v>
@@ -7073,16 +7073,16 @@
         <v>150</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ34" t="n">
         <v>10</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT34" t="n">
         <v>5.9</v>
@@ -7091,44 +7091,44 @@
         <v>6.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ34" t="n">
         <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB34" t="n">
         <v>19.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF34" t="n">
         <v>21</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>1.09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>13.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>200</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.1</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>6.2</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>10</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AK2" t="n">
-        <v>55</v>
+        <v>990</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>990</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AS2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AY2" t="n">
         <v>2.5</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.88</v>
+        <v>2.94</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>1.84</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.6</v>
+        <v>1.84</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.99</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW3" t="n">
         <v>34</v>
       </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AX3" t="n">
-        <v>1.92</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.75</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.49</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.67</v>
+        <v>36</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.24</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.76</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>120</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.76</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1145,40 +1145,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
         <v>3.45</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
@@ -1196,25 +1196,25 @@
         <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1232,83 +1232,83 @@
         <v>950</v>
       </c>
       <c r="AI4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL4" t="n">
         <v>85</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AW4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX4" t="n">
         <v>7</v>
       </c>
-      <c r="AX4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.7</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.7</v>
+        <v>27</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>7.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1387,10 +1387,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
         <v>19</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1533,67 +1533,67 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W6" t="n">
         <v>1.27</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA6" t="n">
         <v>21</v>
@@ -1602,7 +1602,7 @@
         <v>22</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
@@ -1614,13 +1614,13 @@
         <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ6" t="n">
         <v>110</v>
@@ -1629,31 +1629,31 @@
         <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
         <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO6" t="n">
         <v>12.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
         <v>17.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -1665,38 +1665,38 @@
         <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1727,61 +1727,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="n">
         <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W7" t="n">
         <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
         <v>6.6</v>
@@ -1817,64 +1817,64 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AM7" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AN7" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AO7" t="n">
         <v>32</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4</v>
-      </c>
       <c r="AV7" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA7" t="n">
         <v>7.4</v>
       </c>
       <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
         <v>7.8</v>
@@ -1883,14 +1883,14 @@
         <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1921,46 +1921,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="H8" t="n">
         <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
         <v>2.02</v>
@@ -1969,13 +1969,13 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
         <v>20</v>
@@ -2002,7 +2002,7 @@
         <v>11.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
         <v>29</v>
@@ -2023,7 +2023,7 @@
         <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
         <v>190</v>
@@ -2035,10 +2035,10 @@
         <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
         <v>5.9</v>
@@ -2050,7 +2050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -2059,10 +2059,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2071,20 +2071,20 @@
         <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="I9" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>1.19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.4</v>
+        <v>1.19</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>1.19</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.4</v>
+        <v>1.11</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>1.19</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>1.19</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>1.19</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.4</v>
+        <v>1.11</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>1.06</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>1.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>1.19</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>1.11</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>1.11</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.8</v>
+        <v>1.11</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>1.11</v>
       </c>
       <c r="BE9" t="n">
-        <v>7</v>
+        <v>1.11</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
-        <v>18</v>
+        <v>1.05</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.94</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.24</v>
-      </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
@@ -2369,94 +2369,94 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS10" t="n">
         <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.96</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BA10" t="n">
         <v>4.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD10" t="n">
         <v>4</v>
@@ -2465,14 +2465,14 @@
         <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G11" t="n">
         <v>7.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="I11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="J11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.29</v>
@@ -2533,58 +2533,58 @@
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="W11" t="n">
         <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC11" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12</v>
-      </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AF11" t="n">
         <v>100</v>
       </c>
       <c r="AG11" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AH11" t="n">
         <v>34</v>
@@ -2593,80 +2593,80 @@
         <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AK11" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AL11" t="n">
         <v>100</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AO11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
         <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE11" t="n">
         <v>9.6</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BF11" t="n">
         <v>9.4</v>
       </c>
-      <c r="BE11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
         <v>2.16</v>
@@ -2706,13 +2706,13 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
         <v>2.88</v>
       </c>
       <c r="K12" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.67</v>
@@ -2721,31 +2721,31 @@
         <v>1.17</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
         <v>6.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.86</v>
@@ -2754,7 +2754,7 @@
         <v>7.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
@@ -2763,7 +2763,7 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC12" t="n">
         <v>1000</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
@@ -2805,19 +2805,19 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
@@ -2826,41 +2826,41 @@
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BB12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2891,76 +2891,76 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.44</v>
       </c>
-      <c r="I13" t="n">
-        <v>1.56</v>
-      </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="O13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z13" t="n">
         <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>14</v>
@@ -2969,13 +2969,13 @@
         <v>27</v>
       </c>
       <c r="AF13" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AG13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="n">
         <v>110</v>
@@ -2984,10 +2984,10 @@
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2996,10 +2996,10 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>4</v>
@@ -3014,7 +3014,7 @@
         <v>17.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>9.6</v>
@@ -3023,38 +3023,38 @@
         <v>18</v>
       </c>
       <c r="AX13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6</v>
       </c>
-      <c r="AY13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
         <v>6</v>
       </c>
-      <c r="BB13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3085,76 +3085,76 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="H14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
         <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="X14" t="n">
         <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z14" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -3163,10 +3163,10 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -3175,80 +3175,80 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AU14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3279,70 +3279,70 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
         <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="V15" t="n">
         <v>2.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
         <v>17</v>
       </c>
       <c r="Y15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
         <v>24</v>
@@ -3354,13 +3354,13 @@
         <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
         <v>65</v>
       </c>
       <c r="AG15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH15" t="n">
         <v>27</v>
@@ -3369,10 +3369,10 @@
         <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AK15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL15" t="n">
         <v>110</v>
@@ -3381,68 +3381,68 @@
         <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AO15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP15" t="n">
         <v>11</v>
       </c>
-      <c r="AP15" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB15" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB15" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G16" t="n">
         <v>6.8</v>
@@ -3482,7 +3482,7 @@
         <v>1.51</v>
       </c>
       <c r="I16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -3503,34 +3503,34 @@
         <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="W16" t="n">
         <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
         <v>15.5</v>
@@ -3539,104 +3539,104 @@
         <v>18.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK16" t="n">
         <v>75</v>
       </c>
       <c r="AL16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN16" t="n">
         <v>60</v>
       </c>
-      <c r="AM16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>70</v>
-      </c>
       <c r="AO16" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.5</v>
+        <v>26</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="AU16" t="n">
         <v>10.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="AY16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6</v>
-      </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BF16" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
         <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW17" t="n">
         <v>7.8</v>
@@ -3802,7 +3802,7 @@
         <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
         <v>16</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3867,10 +3867,10 @@
         <v>2.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
         <v>3.45</v>
@@ -3885,28 +3885,28 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R18" t="n">
         <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
         <v>1.76</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
         <v>1.37</v>
@@ -3930,7 +3930,7 @@
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
         <v>15.5</v>
@@ -3957,13 +3957,13 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>13</v>
@@ -4005,7 +4005,7 @@
         <v>36</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
         <v>20</v>
@@ -4014,17 +4014,17 @@
         <v>25</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
         <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I19" t="n">
         <v>2.56</v>
@@ -4070,7 +4070,7 @@
         <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -4079,25 +4079,25 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
         <v>1.84</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
         <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
         <v>2.28</v>
@@ -4106,61 +4106,61 @@
         <v>1.64</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>15</v>
-      </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
         <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ19" t="n">
         <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
         <v>32</v>
       </c>
       <c r="AO19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP19" t="n">
         <v>14.5</v>
@@ -4178,7 +4178,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
@@ -4187,7 +4187,7 @@
         <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AY19" t="n">
         <v>12</v>
@@ -4196,19 +4196,19 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.3</v>
+        <v>29</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BF19" t="n">
         <v>22</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>3.6</v>
@@ -4279,28 +4279,28 @@
         <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
         <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U20" t="n">
         <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
         <v>15</v>
@@ -4309,37 +4309,37 @@
         <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
         <v>48</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AF20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
         <v>27</v>
@@ -4348,13 +4348,13 @@
         <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
         <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
         <v>14</v>
@@ -4363,13 +4363,13 @@
         <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
@@ -4381,28 +4381,28 @@
         <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY20" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
         <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
         <v>32</v>
       </c>
       <c r="BE20" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BF20" t="n">
         <v>18.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G21" t="n">
         <v>3.2</v>
       </c>
-      <c r="G21" t="n">
-        <v>3.35</v>
-      </c>
       <c r="H21" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="J21" t="n">
         <v>3.8</v>
@@ -4461,10 +4461,10 @@
         <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4476,7 +4476,7 @@
         <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R21" t="n">
         <v>1.54</v>
@@ -4491,31 +4491,31 @@
         <v>2.52</v>
       </c>
       <c r="V21" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="W21" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X21" t="n">
         <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4533,25 +4533,25 @@
         <v>32</v>
       </c>
       <c r="AJ21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
         <v>65</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO21" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
@@ -4560,7 +4560,7 @@
         <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -4575,38 +4575,38 @@
         <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BC21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="BG21" t="n">
         <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.58</v>
       </c>
       <c r="G22" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H22" t="n">
         <v>2.78</v>
       </c>
       <c r="I22" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
@@ -4682,13 +4682,13 @@
         <v>1.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X22" t="n">
         <v>19.5</v>
@@ -4742,65 +4742,65 @@
         <v>970</v>
       </c>
       <c r="AO22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX22" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>6</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H23" t="n">
         <v>6.2</v>
       </c>
       <c r="I23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.59</v>
@@ -4876,13 +4876,13 @@
         <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="V23" t="n">
         <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X23" t="n">
         <v>10.5</v>
@@ -4969,7 +4969,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BA23" t="n">
         <v>4.9</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -5016,73 +5016,73 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="S24" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5091,13 +5091,13 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
@@ -5106,7 +5106,7 @@
         <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
         <v>1000</v>
@@ -5133,69 +5133,69 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.12</v>
+        <v>4.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.13</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.13</v>
+        <v>6.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.06</v>
+        <v>6.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.13</v>
+        <v>5.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.06</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.12</v>
+        <v>4.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.13</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.13</v>
+        <v>32</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.13</v>
+        <v>5.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.13</v>
+        <v>5.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>32</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.95</v>
       </c>
-      <c r="J25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="U25" t="n">
-        <v>1.69</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="Y25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY25" t="n">
         <v>9.6</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.1</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.2</v>
+        <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>VST Volkermarkt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>SV Spittal/Drau</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R26" t="n">
         <v>2</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="S26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X26" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN26" t="n">
         <v>3.95</v>
       </c>
-      <c r="I26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X26" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>12</v>
-      </c>
       <c r="AO26" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.78</v>
+        <v>2.86</v>
       </c>
       <c r="G27" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>2.58</v>
       </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>2.74</v>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.56</v>
+        <v>3.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>8.6</v>
       </c>
       <c r="T27" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>2.58</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W27" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE27" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.8</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>21</v>
+        <v>1.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.6</v>
+        <v>1.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>15.5</v>
+        <v>1.13</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>12.5</v>
+        <v>1.13</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.4</v>
+        <v>1.12</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13.5</v>
+        <v>1.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>17.5</v>
+        <v>1.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>14.5</v>
+        <v>1.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>17</v>
+        <v>1.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="G28" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="H28" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.29</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="R28" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S28" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U28" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V28" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="X28" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Y28" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Z28" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB28" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC28" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>22</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="AR28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW28" t="n">
         <v>23</v>
       </c>
-      <c r="AK28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AX28" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE28" t="n">
         <v>15</v>
       </c>
-      <c r="BB28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD28" t="n">
+      <c r="BF28" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG28" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="G29" t="n">
-        <v>3.35</v>
+        <v>1.96</v>
       </c>
       <c r="H29" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>2.48</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K29" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="T29" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="U29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W29" t="n">
         <v>2.04</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X29" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="Z29" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI29" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ29" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO29" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE29" t="n">
         <v>10</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>100</v>
-      </c>
       <c r="BF29" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>24</v>
+        <v>5.7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.14</v>
+        <v>3.35</v>
       </c>
       <c r="G30" t="n">
-        <v>1.16</v>
+        <v>3.4</v>
       </c>
       <c r="H30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X30" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO30" t="n">
         <v>26</v>
       </c>
-      <c r="I30" t="n">
-        <v>29</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="AP30" t="n">
         <v>10.5</v>
       </c>
-      <c r="K30" t="n">
+      <c r="AQ30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV30" t="n">
         <v>11</v>
       </c>
-      <c r="L30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>340</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>530</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG30" t="n">
+      <c r="AW30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY30" t="n">
         <v>14</v>
       </c>
-      <c r="AH30" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>320</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL30" t="n">
+      <c r="AZ30" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF30" t="n">
         <v>42</v>
       </c>
-      <c r="AM30" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>2.64</v>
-      </c>
       <c r="BG30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.84</v>
+        <v>1.14</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>1.15</v>
       </c>
       <c r="H31" t="n">
-        <v>1.09</v>
+        <v>26</v>
       </c>
       <c r="I31" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.24</v>
+        <v>8.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="P31" t="n">
-        <v>1.23</v>
+        <v>3.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="R31" t="n">
-        <v>1.13</v>
+        <v>1.98</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>1.98</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>5.1</v>
+        <v>1.23</v>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="K32" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="G33" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="H33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
         <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P33" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>1.83</v>
       </c>
       <c r="V33" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y33" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA33" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD33" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK33" t="n">
         <v>25</v>
       </c>
-      <c r="AE33" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>27</v>
-      </c>
       <c r="AL33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM33" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AO33" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="AX33" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AY33" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="BB33" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,184 +6951,378 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="G34" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="H34" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="O34" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="P34" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="V34" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W34" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Z34" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA34" t="n">
         <v>150</v>
       </c>
       <c r="AB34" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI34" t="n">
         <v>100</v>
       </c>
-      <c r="AF34" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI34" t="n">
+      <c r="AJ34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO34" t="n">
         <v>120</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>150</v>
-      </c>
       <c r="AP34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AQ34" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU34" t="n">
         <v>6.4</v>
       </c>
       <c r="AV34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW34" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AX34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-29 04:55:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC35" t="n">
         <v>6</v>
       </c>
-      <c r="AX34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF34" t="n">
+      <c r="BD35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF35" t="n">
         <v>21</v>
       </c>
-      <c r="BG34" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-04-29 02:46:56</t>
+      <c r="BG35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,54 +743,54 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>05:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hubei Istar</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Shanghai Second</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17.5</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.42</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1.46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>2.48</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
         <v>1.02</v>
@@ -799,49 +799,49 @@
         <v>36</v>
       </c>
       <c r="T2" t="n">
-        <v>2.26</v>
+        <v>4.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>3.15</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.06</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.2</v>
+        <v>990</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>120</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -850,7 +850,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -865,69 +865,69 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>3.35</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="AS2" t="n">
-        <v>50</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>2.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AW2" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AZ2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA2" t="n">
         <v>65</v>
       </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="BE2" t="n">
-        <v>17.5</v>
+        <v>46</v>
       </c>
       <c r="BF2" t="n">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,112 +942,112 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Shandong Taishan B</t>
+          <t>Chiangrai Utd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai Second</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>4.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>2.84</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,72 +1056,72 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.06</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.06</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.06</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.06</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.06</v>
+        <v>55</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.06</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.06</v>
+        <v>27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.06</v>
+        <v>55</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.06</v>
+        <v>140</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.06</v>
+        <v>140</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.06</v>
+        <v>130</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.06</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.06</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.06</v>
+        <v>65</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Chiangrai Utd</t>
+          <t>Ganzhou Ruishi FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Xiamen Feilu</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="I4" t="n">
-        <v>1.96</v>
+        <v>1.34</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="AA4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>130</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>240</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG4" t="n">
         <v>22</v>
       </c>
-      <c r="AB4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ganzhou Ruishi FC</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xiamen Feilu</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>1.31</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>1.35</v>
       </c>
       <c r="H5" t="n">
-        <v>1.97</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>2.14</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
         <v>5.3</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>15</v>
-      </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>260</v>
       </c>
       <c r="AF5" t="n">
-        <v>34</v>
+        <v>5.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="AH5" t="n">
         <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="AK5" t="n">
-        <v>85</v>
+        <v>17.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="AN5" t="n">
-        <v>150</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>32</v>
+        <v>550</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>95</v>
+      </c>
+      <c r="BB5" t="n">
         <v>10</v>
       </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>160</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Guizhou Zhucheng Athletic</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Bangkok Utd</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="N6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.1</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>640</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG6" t="n">
         <v>25</v>
       </c>
-      <c r="AE6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AI6" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>300</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY6" t="n">
         <v>20</v>
       </c>
-      <c r="AK6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.800000000000001</v>
+        <v>130</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.5</v>
+        <v>100</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>90</v>
       </c>
       <c r="BD6" t="n">
-        <v>32</v>
+        <v>210</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>500</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bangkok Utd</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>1.37</v>
       </c>
       <c r="H7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.04</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.94</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>3.7</v>
       </c>
       <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="BD7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>48</v>
-      </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>140</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>Buriram Utd</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.62</v>
+        <v>6.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>1.54</v>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.1</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>2.7</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW8" t="n">
         <v>14</v>
       </c>
-      <c r="Y8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AX8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>60</v>
       </c>
-      <c r="AA8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL8" t="n">
+      <c r="BD8" t="n">
         <v>60</v>
       </c>
-      <c r="AM8" t="n">
-        <v>600</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="BE8" t="n">
         <v>10</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="BF8" t="n">
+        <v>60</v>
+      </c>
+      <c r="BG8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Buriram Utd</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>8.800000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="H9" t="n">
-        <v>1.44</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7</v>
+        <v>2.94</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="N9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT9" t="n">
         <v>5.9</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX9" t="n">
         <v>11</v>
       </c>
-      <c r="AA9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AY9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD9" t="n">
         <v>46</v>
       </c>
-      <c r="AC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="BE9" t="n">
         <v>15</v>
       </c>
-      <c r="AF9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,184 +2295,184 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>AS Solimane</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="J10" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>2.94</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="M10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Z10" t="n">
         <v>7</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AC10" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="AZ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA10" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BB10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AS Solimane</t>
+          <t>US Monastirienne</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>AS Gabes</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12.5</v>
+        <v>1.37</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>1.41</v>
       </c>
       <c r="H11" t="n">
-        <v>1.41</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>1.46</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
         <v>5.4</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AA11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>560</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AV11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD11" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tunisian Ligue Professionelle 1</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>US Monastirienne</t>
+          <t>NK Jadran Dekani</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Gabes</t>
+          <t>NK Brinje Grosuplje</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1.41</v>
+        <v>9.4</v>
       </c>
       <c r="H12" t="n">
-        <v>14.5</v>
+        <v>1.51</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>1.53</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>2.84</v>
       </c>
       <c r="W12" t="n">
-        <v>3.45</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>310</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>210</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS12" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AT12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA12" t="n">
         <v>34</v>
       </c>
-      <c r="Z12" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="BB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>11</v>
       </c>
-      <c r="AK12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>17</v>
-      </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NK Jadran Dekani</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NK Brinje Grosuplje</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="I13" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X13" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5.1</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>410</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>210</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>170</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>320</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU14" t="n">
         <v>7.4</v>
       </c>
-      <c r="H14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X14" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AV14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>14.5</v>
       </c>
-      <c r="AB14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="BA14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>13</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>2.42</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.38</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.81</v>
-      </c>
       <c r="X15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH15" t="n">
         <v>19.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>42</v>
+        <v>6.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB15" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC15" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="BD15" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>2.44</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.41</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="X16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG16" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AH16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AI16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL16" t="n">
         <v>38</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AM16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>12</v>
       </c>
-      <c r="AC16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AR16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW16" t="n">
         <v>32</v>
       </c>
-      <c r="AF16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AX16" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BF16" t="n">
-        <v>38</v>
+        <v>16.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="H17" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W17" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW17" t="n">
         <v>21</v>
       </c>
-      <c r="AA17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AX17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY17" t="n">
         <v>12</v>
       </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX17" t="n">
+      <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG17" t="n">
         <v>15.5</v>
       </c>
-      <c r="AY17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>23</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="n">
         <v>2.4</v>
       </c>
       <c r="I18" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
         <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
         <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ18" t="n">
         <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP18" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX18" t="n">
         <v>21</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.6</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BD18" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG18" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.98</v>
+        <v>2.52</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="H19" t="n">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="I19" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE19" t="n">
         <v>55</v>
       </c>
-      <c r="AB19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW19" t="n">
         <v>12</v>
       </c>
-      <c r="AE19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BE19" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BF19" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.58</v>
+        <v>1.79</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="H20" t="n">
-        <v>2.78</v>
+        <v>5.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV20" t="n">
         <v>21</v>
       </c>
-      <c r="AA20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AW20" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AX20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC20" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB20" t="n">
+      <c r="BD20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE20" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF20" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>VST Volkermarkt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>SV Spittal/Drau</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S21" t="n">
         <v>1.78</v>
       </c>
-      <c r="G21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="T21" t="n">
         <v>1.59</v>
       </c>
-      <c r="M21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>2.32</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="Z21" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AA21" t="n">
         <v>270</v>
       </c>
       <c r="AB21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS21" t="n">
         <v>6.2</v>
       </c>
-      <c r="AC21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AT21" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD21" t="n">
         <v>20</v>
       </c>
-      <c r="BD21" t="n">
-        <v>7</v>
-      </c>
       <c r="BE21" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BF21" t="n">
-        <v>17</v>
+        <v>2.82</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VST Volkermarkt</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SV Spittal/Drau</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37</v>
+        <v>3.35</v>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>2.98</v>
       </c>
       <c r="I22" t="n">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>5.9</v>
+        <v>2.66</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6</v>
+        <v>2.78</v>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="N22" t="n">
-        <v>8.199999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.31</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="S22" t="n">
-        <v>1.77</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>3.5</v>
+        <v>1.42</v>
       </c>
       <c r="X22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>13</v>
+        <v>1.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>10</v>
+        <v>1.13</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>1.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>19</v>
+        <v>1.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.84</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -4822,19 +4822,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="H23" t="n">
         <v>3.4</v>
@@ -4843,52 +4843,52 @@
         <v>3.6</v>
       </c>
       <c r="J23" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="K23" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="L23" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="M23" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="O23" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="P23" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V23" t="n">
         <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,13 +4897,13 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4912,10 +4912,10 @@
         <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4939,69 +4939,69 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.13</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.13</v>
+        <v>7.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.13</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.13</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.13</v>
+        <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.06</v>
+        <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.13</v>
+        <v>23</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.13</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.06</v>
+        <v>12</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.13</v>
+        <v>10.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.13</v>
+        <v>8.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.13</v>
+        <v>32</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.13</v>
+        <v>8.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>36</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>2.46</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>1.45</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S24" t="n">
-        <v>6.4</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="U24" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="V24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="X24" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AC24" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV24" t="n">
         <v>15</v>
       </c>
-      <c r="AG24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AW24" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AX24" t="n">
         <v>12</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="G25" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.26</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>2.3</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="X25" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>16</v>
-      </c>
       <c r="AE25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF25" t="n">
         <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP25" t="n">
         <v>23</v>
       </c>
-      <c r="AK25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL25" t="n">
+      <c r="AQ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR25" t="n">
         <v>32</v>
       </c>
-      <c r="AM25" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="n">
+      <c r="AS25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT25" t="n">
         <v>12</v>
       </c>
-      <c r="AO25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AU25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV25" t="n">
         <v>16</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>15</v>
       </c>
       <c r="AW25" t="n">
         <v>38</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BC25" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BE25" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF25" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R26" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
         <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V26" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="X26" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Y26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z26" t="n">
         <v>34</v>
       </c>
-      <c r="Z26" t="n">
-        <v>44</v>
-      </c>
       <c r="AA26" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
         <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AM26" t="n">
         <v>65</v>
       </c>
       <c r="AN26" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO26" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AP26" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG26" t="n">
         <v>24</v>
       </c>
-      <c r="AR26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>32</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="G27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.98</v>
       </c>
-      <c r="H27" t="n">
-        <v>4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.56</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="W27" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="X27" t="n">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="Z27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS27" t="n">
         <v>34</v>
       </c>
-      <c r="AA27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AT27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC27" t="n">
         <v>40</v>
       </c>
-      <c r="AF27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL27" t="n">
+      <c r="BD27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>48</v>
+      </c>
+      <c r="BG27" t="n">
         <v>25</v>
       </c>
-      <c r="AM27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>18</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>1.14</v>
       </c>
       <c r="G28" t="n">
-        <v>3.35</v>
+        <v>1.15</v>
       </c>
       <c r="H28" t="n">
-        <v>2.46</v>
+        <v>27</v>
       </c>
       <c r="I28" t="n">
-        <v>2.48</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.34</v>
+        <v>1.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.98</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="V28" t="n">
-        <v>1.67</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.42</v>
+        <v>7.8</v>
       </c>
       <c r="X28" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>380</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>490</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT28" t="n">
         <v>11</v>
       </c>
-      <c r="Y28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="AU28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD28" t="n">
         <v>36</v>
       </c>
-      <c r="AB28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>50</v>
-      </c>
       <c r="BE28" t="n">
-        <v>100</v>
+        <v>16.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>42</v>
+        <v>2.68</v>
       </c>
       <c r="BG28" t="n">
         <v>24</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="G29" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="H29" t="n">
-        <v>26</v>
+        <v>5.9</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="K29" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="P29" t="n">
-        <v>3.5</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="W29" t="n">
-        <v>7.6</v>
+        <v>2.42</v>
       </c>
       <c r="X29" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="Y29" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AD29" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE29" t="n">
-        <v>490</v>
+        <v>130</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AI29" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AK29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM29" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.8</v>
+        <v>970</v>
       </c>
       <c r="AO29" t="n">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>36</v>
+        <v>5.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>11.5</v>
+        <v>1.65</v>
       </c>
       <c r="AT29" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AU29" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="AV29" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ29" t="n">
-        <v>38</v>
+        <v>2.04</v>
       </c>
       <c r="BA29" t="n">
-        <v>11.5</v>
+        <v>1.64</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD29" t="n">
-        <v>36</v>
+        <v>3.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>11</v>
+        <v>1.65</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.68</v>
+        <v>13</v>
       </c>
       <c r="BG29" t="n">
-        <v>20</v>
+        <v>1.65</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,54 +6175,54 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="H30" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
         <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R30" t="n">
         <v>1.27</v>
@@ -6231,135 +6231,135 @@
         <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="X30" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="n">
         <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB30" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE30" t="n">
         <v>130</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ30" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN30" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>9.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW30" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW30" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AX30" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.56</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.94</v>
+        <v>4.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="BF30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,378 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="G31" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.5</v>
       </c>
-      <c r="K31" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="P31" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="X31" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA31" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC31" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC31" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF31" t="n">
         <v>12.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ31" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN31" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AO31" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT31" t="n">
         <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Internacional de Palmira</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,153 +781,153 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,766 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW3" t="n">
         <v>26</v>
       </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>150</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AX3" t="n">
-        <v>1.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>48</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>17:30:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Envigado</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Tigres FC Zipaquira</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>520</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>270</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>280</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-04-29 18:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Uruguayan Segunda Division</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CA Rentistas</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Miramar Misiones</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-04-29 18:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Internacional de Palmira</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,378 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.23</v>
+        <v>3.25</v>
       </c>
       <c r="G2" t="n">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6</v>
+        <v>1.77</v>
       </c>
       <c r="K2" t="n">
-        <v>6.4</v>
+        <v>1.81</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="N2" t="n">
-        <v>2.56</v>
+        <v>1.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.95</v>
+        <v>40</v>
       </c>
       <c r="R2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>14.5</v>
+        <v>200</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>9.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>4.8</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.72</v>
+        <v>4.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="AE2" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>120</v>
       </c>
       <c r="AH2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.5</v>
+        <v>290</v>
       </c>
       <c r="AK2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>46</v>
-      </c>
       <c r="BF2" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Internacional de Palmira</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
